--- a/CV_data.xlsx
+++ b/CV_data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/38c30cdae7cc714a/Desktop/Portfolio/cv_data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yambs\OneDrive\Desktop\Portfolio\cv_dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="303" documentId="11_A70B9B3F86F56A9DBC05FC0EF6B42A862AA9A020" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1842B4EF-5594-40A9-9C3A-13C06FBA5531}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADB2ED04-457D-45F2-8988-AA0FF3CE852C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="718" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="718" firstSheet="7" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="type_of_work" sheetId="1" r:id="rId1"/>
@@ -23,13 +23,132 @@
     <sheet name="publications" sheetId="8" r:id="rId8"/>
     <sheet name="bridge_project_software" sheetId="9" r:id="rId9"/>
     <sheet name="data_used" sheetId="10" r:id="rId10"/>
+    <sheet name="positions_of_trust" sheetId="11" r:id="rId11"/>
+    <sheet name="required_expertise" sheetId="12" r:id="rId12"/>
+    <sheet name="bridge_project_data" sheetId="13" r:id="rId13"/>
+    <sheet name="bridge_project_expertise" sheetId="14" r:id="rId14"/>
+    <sheet name="bridge_expertise_core_skill" sheetId="15" r:id="rId15"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1115" uniqueCount="554">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1193" uniqueCount="588">
+  <si>
+    <t>id_pub</t>
+  </si>
+  <si>
+    <t>Citation</t>
+  </si>
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>Publisher/Journal</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Desalegn, Y. (2020). Off-farm Activities, Incomes and Household Welfare in Rural Ethiopia. Addis Ababa University and JIBS, Ethiopia under the supervision of Almas Heshmati (PhD), Jonkoping International Business School (JIBS), Jonkoping University, Sweden, and Adane Tufa (PhD), Department of Economics, Addis Ababa University (AAU), Ethiopia</t>
+  </si>
+  <si>
+    <t>Off-farm Activities, Incomes and Household Welfare in Rural Ethiopia</t>
+  </si>
+  <si>
+    <t>Addis Ababa University &amp; Jönköping University (Dissertation)</t>
+  </si>
+  <si>
+    <t>PhD Dissertation</t>
+  </si>
+  <si>
+    <t>Desalegn, Y. (2018). Returns to education in Ethiopia. In Economic Growth and Development in Ethiopia (pp. 199-226). Springer, Singapore.</t>
+  </si>
+  <si>
+    <t>Returns to education in Ethiopia</t>
+  </si>
+  <si>
+    <t>Springer, Singapore (Book Chapter)</t>
+  </si>
+  <si>
+    <t>Book Chapter</t>
+  </si>
+  <si>
+    <t>Tegegn, T., Paulos, M., &amp; Desalegn, Y. (2016). Determinants of Entrepreneurial Intention among Prospective Graduates of Higher Institutions Case of Wolaita Sodo University. Journal of Education and Practice, 7(16), 46-53.</t>
+  </si>
+  <si>
+    <t>Determinants of Entrepreneurial Intention among Prospective Graduates of Higher Institutions Case of Wolaita Sodo University</t>
+  </si>
+  <si>
+    <t>Journal of Education and Practice</t>
+  </si>
+  <si>
+    <t>Journal Article</t>
+  </si>
+  <si>
+    <t>Amphune, B. E., Weldegebriel, Z. B., &amp; Enaro, Y. D. (2018). Migration and Urban Livelihoods: A Quest for Sustainability in Southern Ethiopia.</t>
+  </si>
+  <si>
+    <t>Migration and Urban Livelihoods: A Quest for Sustainability in Southern Ethiopia</t>
+  </si>
+  <si>
+    <t>Unpublished/Other</t>
+  </si>
+  <si>
+    <t>Kassie, G.T., Y. Desalegn, W. Asnake, A. Haile, and B. Rischkowsky. (2021). Synthesis report on critical challenges and necessary strategic shifts in livestock market development in Ethiopia. Working Paper. ICARDA (International Center for Agricultural Research in the Dry Areas). Beirut, Lebanon.</t>
+  </si>
+  <si>
+    <t>Synthesis report on critical challenges and necessary strategic shifts in livestock market development in Ethiopia</t>
+  </si>
+  <si>
+    <t>ICARDA Working Paper</t>
+  </si>
+  <si>
+    <t>Working Paper</t>
+  </si>
+  <si>
+    <t>Girma Kassie, Aynalem Haile, Woinishet Asnake, Yonatan Desalegn, Barbara Rischkowsky. (2021). Impact of Community-based breeding program on the performance of and income from small ruminants in Ethiopia. Working Paper. CGIAR-ICARDA.</t>
+  </si>
+  <si>
+    <t>Impact of Community-based breeding program on the performance of and income from small ruminants in Ethiopia</t>
+  </si>
+  <si>
+    <t>CGIAR-ICARDA Working Paper</t>
+  </si>
+  <si>
+    <t>Mamo, Tigist; Tadesse, Elazar; Oranga, Beryl; Desalegn, Yonatan; Tumusiime, Emmanuel; Kirby, Miles; Reider, Kathryn; Wagg, Michael. (2026). Empowering Caregivers to Assess and Evaluate Child Nutrition Outcomes: A Pilot Study from Rural Ethiopia. Working paper. Ninth International CREA Conference</t>
+  </si>
+  <si>
+    <t>Empowering Caregivers to Assess and Evaluate Child Nutrition Outcomes: A Pilot Study from Rural Ethiopia</t>
+  </si>
+  <si>
+    <t>Ninth International CREA Conference</t>
+  </si>
+  <si>
+    <t>Conference paper</t>
+  </si>
+  <si>
+    <t>Tigist M.Cherkos, Elazar T. Balla, Yonatan D.Enaro, Miles Kirby, Precious M. Mubanga, Beryl A. Oranga, Kathryn Reider, Emmanuel Tumusiime. (2026). Impact of Family MUAC Training and Supervision Intensity on Caregivers Accuracy and Cost‑Effectiveness in Rural Ethiopia. Conference paper. Nutrition 2026</t>
+  </si>
+  <si>
+    <t>Impact of Family MUAC Training and Supervision Intensity on Caregivers Accuracy and Cost‑Effectiveness in Rural Ethiopia</t>
+  </si>
+  <si>
+    <t>Nutrition 2026 conference of American Society of Nutrition</t>
+  </si>
+  <si>
+    <t>Yonatan Desalegn and Tamrate Woldemariam. (2026) Child labor and schooling outcomes - a cross continent analysis. Forthcoming</t>
+  </si>
+  <si>
+    <t>Child labor and schooling outcomes - a cross continent analysis</t>
+  </si>
+  <si>
+    <t>Research manuscript</t>
+  </si>
   <si>
     <t>id_prj</t>
   </si>
@@ -37,9 +156,6 @@
     <t>Long title</t>
   </si>
   <si>
-    <t>Title</t>
-  </si>
-  <si>
     <t>type</t>
   </si>
   <si>
@@ -97,6 +213,9 @@
     <t>FGD count</t>
   </si>
   <si>
+    <t>Most Significant Change (MSC)</t>
+  </si>
+  <si>
     <t>Benchmarking</t>
   </si>
   <si>
@@ -115,6 +234,9 @@
     <t>Report url</t>
   </si>
   <si>
+    <t>GitHub rep</t>
+  </si>
+  <si>
     <t>Report size</t>
   </si>
   <si>
@@ -169,6 +291,12 @@
     <t>Capacity Development Expert</t>
   </si>
   <si>
+    <t>Monitoring &amp; Evaluation</t>
+  </si>
+  <si>
+    <t>Monitoring &amp; Evaluation (M&amp;E); Advanced Statistical Analysis &amp; Econometrics; Thematic Qualitative Analysis; Survey Design, ODK/XLSForms &amp; Data Collection</t>
+  </si>
+  <si>
     <t>Kobo, Stata</t>
   </si>
   <si>
@@ -208,229 +336,250 @@
     <t>giulietta.delli@timesis.it</t>
   </si>
   <si>
+    <t>Research</t>
+  </si>
+  <si>
+    <t>Operations Research and Formative Assessment on Multisectoral Nutrition Coordination of Ethiopia</t>
+  </si>
+  <si>
+    <t>MSC assessment</t>
+  </si>
+  <si>
+    <t>Research Associate</t>
+  </si>
+  <si>
+    <t>Advanced Statistical Analysis &amp; Econometrics; Thematic Qualitative Analysis</t>
+  </si>
+  <si>
+    <t>Mar 2021 - Apr 2021</t>
+  </si>
+  <si>
+    <t>This operational research on multi-sectoral nutrition coordination in Ethiopia, supported by UNICEF and the World Bank, assessed coordination mechanisms across various government levels and sectors, identifying bottlenecks and proposing innovative strategies for better nutrition outcomes.</t>
+  </si>
+  <si>
+    <t>conducting nine high-level Key Informant Interviews (KIIs), transcribing, and summarizing the interviews.</t>
+  </si>
+  <si>
+    <t>the qualitative data collected informed the design and establishment of a MSC mechanism for Ethiopia, ensuring lessons learned were addressed across sectors.</t>
+  </si>
+  <si>
+    <t>UNICEF Ethiopia</t>
+  </si>
+  <si>
+    <t>Mesfin Beyero</t>
+  </si>
+  <si>
+    <t>drbeyero@gmail.com</t>
+  </si>
+  <si>
+    <t>Situation Analysis and Baseline Study for EnJOY project</t>
+  </si>
+  <si>
+    <t>ENJOY project baseline</t>
+  </si>
+  <si>
+    <t>Baseline</t>
+  </si>
+  <si>
+    <t>M &amp; E Expert</t>
+  </si>
+  <si>
+    <t>Baseline Assessment</t>
+  </si>
+  <si>
+    <t>Data Cleaning, Management &amp; Integration; Advanced Statistical Analysis &amp; Econometrics; Thematic Qualitative Analysis; Survey Design, ODK/XLSForms &amp; Data Collection</t>
+  </si>
+  <si>
+    <t>Stata,  Excel</t>
+  </si>
+  <si>
+    <t>Apr 2021 - Jun 2021</t>
+  </si>
+  <si>
+    <t>The EnJOY – (Enhancing Job Opportunities and Employability for Youth and women) project aims to enhance job opportunities for youth and women in Oromia, Sidama, and SNNP regions by improving access to employment information, supporting service delivery, and fostering multi-sectoral collaboration.</t>
+  </si>
+  <si>
+    <t>analyzing and interpreting qualitative and quantitative data (519 survey data points, 80 KIIs, and 40 FGDs) using Stata and Nvivo, populating the project logframe with baseline, and report writeup.</t>
+  </si>
+  <si>
+    <t>supplied project KPIs with baseline data to inform progress along the project logic indicators, identified operational level gaps existing in the job creation space; lack of multisectoral coordination and poor skills training programs identified as learnings, which informed the program and used this feedback to modify its interventions.</t>
+  </si>
+  <si>
+    <t>CARITAS Switzerland</t>
+  </si>
+  <si>
+    <t>European Union</t>
+  </si>
+  <si>
+    <t>Dereje Getu</t>
+  </si>
+  <si>
+    <t>dereje.getu@dabdrt.com</t>
+  </si>
+  <si>
+    <t>Evaluation</t>
+  </si>
+  <si>
+    <t>Africa RISING</t>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t>Literature analyst</t>
+  </si>
+  <si>
+    <t>Economic Research</t>
+  </si>
+  <si>
+    <t>Data Cleaning, Management &amp; Integration; Advanced Statistical Analysis &amp; Econometrics; Data Visualization &amp; Reporting</t>
+  </si>
+  <si>
+    <t>May 2021 - Dec 2021</t>
+  </si>
+  <si>
+    <t>The Africa RISING project aims to enhance smallholder farmers’ livelihoods by increasing productivity, diversifying cropping systems, and mitigating climate risks. It focuses on sustainable intensification, bridging food gaps, and improving crop and livestock integration.</t>
+  </si>
+  <si>
+    <t>responsible for reviewing and synthesizing literature for six potential research articles and developing empirical methodologies to address the associated research question</t>
+  </si>
+  <si>
+    <t>produced and submitted a technical note to the Ministry of Agriculture on the necessary shifts required to improve the livestock market in Ethiopia and produced two research articles</t>
+  </si>
+  <si>
+    <t>ICARDA</t>
+  </si>
+  <si>
+    <t>Girma T. Kassie</t>
+  </si>
+  <si>
+    <t>g.tesfahun@cgiar.org</t>
+  </si>
+  <si>
+    <t>Systematic literature review</t>
+  </si>
+  <si>
+    <t>Integrated Urban PSNP Baseline Survey</t>
+  </si>
+  <si>
+    <t>UPSNP baseline survey</t>
+  </si>
+  <si>
+    <t>Data quality control expert</t>
+  </si>
+  <si>
+    <t>Data Quality Assurance</t>
+  </si>
+  <si>
+    <t>Data Cleaning, Management &amp; Integration; Advanced Statistical Analysis &amp; Econometrics; Survey Design, ODK/XLSForms &amp; Data Collection</t>
+  </si>
+  <si>
+    <t>Apr 2021 - Aug 2021</t>
+  </si>
+  <si>
+    <t>This is a study of the socio-economic conditions of urban Productive Safety Net Program (PSNP) households. The baseline survey used household, health facility, and community surveys to profile beneficiaries of the IUSNP.</t>
+  </si>
+  <si>
+    <t>quality control and managing survey of 4,050 client households, nineteen health centers, and 143 communities using Stata. I provided training for enumerators on three different multi-module questionnaires, monitored data quality and collection progress, and prepared field progress and exit report</t>
+  </si>
+  <si>
+    <t>data collected was used to inform progress of the integrated urban PSNP program, we used the child-focused modules to determine the role of PSNP on children who belonged to the poorest of the poor in Addis Ababa</t>
+  </si>
+  <si>
+    <t>UNICEF Innocenti</t>
+  </si>
+  <si>
+    <t>Kaku Attah Damoah</t>
+  </si>
+  <si>
+    <t>kdamoah@unicef.org</t>
+  </si>
+  <si>
+    <t>Business Analytics</t>
+  </si>
+  <si>
+    <t>Behavioral Insight study survey for household solid waste segregation</t>
+  </si>
+  <si>
+    <t>BI study - waste seggregation</t>
+  </si>
+  <si>
+    <t>Researcher</t>
+  </si>
+  <si>
+    <t>Data Cleaning, Management &amp; Integration; Data Visualization &amp; Reporting; Survey Design, ODK/XLSForms &amp; Data Collection</t>
+  </si>
+  <si>
+    <t>Jun 2021 - Aug 2021</t>
+  </si>
+  <si>
+    <t>The study looked at residential solid waste segregation behavior in Addis Ababa city.</t>
+  </si>
+  <si>
+    <t>designing methodology tool for the behavioral insights study, field survey and data management (1,503 survey data points, twenty-five waste transfer stations, and 3 FGDs) using the Kobo Toolbox, insights report writeup and validation presentation for the client.</t>
+  </si>
+  <si>
+    <t>identified important insights which included type and volume of solid waste of the city, patterns of segregation, moving, landfills, and point of collaboration between the government and private actors to improve waste collection and disposal.</t>
+  </si>
+  <si>
+    <t>Accelerator Lab</t>
+  </si>
+  <si>
+    <t>UNDP Ethiopia</t>
+  </si>
+  <si>
+    <t>Amanuel Tadesse</t>
+  </si>
+  <si>
+    <t>amanuel.tadesse@undp.org</t>
+  </si>
+  <si>
+    <t>Food Environment Analysis (FEA) – Ethiopia</t>
+  </si>
+  <si>
+    <t>Food Environment Analysis</t>
+  </si>
+  <si>
+    <t>Survey manager</t>
+  </si>
+  <si>
+    <t>Data Cleaning, Management &amp; Integration; Advanced Statistical Analysis &amp; Econometrics; Spatial Data Analysis (GIS); Survey Design, ODK/XLSForms &amp; Data Collection</t>
+  </si>
+  <si>
+    <t>Stata,  Excel, ArcGIS</t>
+  </si>
+  <si>
+    <t>Oct 2021 - Dec 2021</t>
+  </si>
+  <si>
+    <t>Nationwide exploratory research of the food environment in Ethiopia using qualitative and quantitative data. The research explored components of the food systems - personal and external domains.</t>
+  </si>
+  <si>
+    <t>analyzing the 2018/19 ESS/LSMS-ISA data to identify food items consumed disaggregated by all major regions and 10 selected representative Woredas (6,670 data points), for selecting Woredas for the qualitative survey based on the food items identified from the quantitative data analysis (19 FGDs, and 81 KIIs), provide training for qualitative research associates, generate map visualization using ArcGIS, verify data quality and participate in the production of a presentation</t>
+  </si>
+  <si>
+    <t>tested the FEA tool of ACDI/VOCA, profiled the food environment in Ethiopia, identified gaps in terms of dietary intakes, food desirability, affordability, accessibility, and nutrition knowledge presented the result to USAID. These gaps warrant introducing project-based interventions to improve the food environment. We made a pitch to USAID.</t>
+  </si>
+  <si>
+    <t>ACDI/VOCA</t>
+  </si>
+  <si>
+    <t>Alysa Grude</t>
+  </si>
+  <si>
+    <t>AGrude@acdivoca.org</t>
+  </si>
+  <si>
+    <t>A Skill Gap Assessment and Identification of Qualification and Occupation</t>
+  </si>
+  <si>
+    <t>Skill gap assessment</t>
+  </si>
+  <si>
     <t>Lead consultant</t>
   </si>
   <si>
-    <t>Research</t>
-  </si>
-  <si>
-    <t>Operations Research and Formative Assessment on Multisectoral Nutrition Coordination of Ethiopia</t>
-  </si>
-  <si>
-    <t>MSC assessment</t>
-  </si>
-  <si>
-    <t>Research Associate</t>
-  </si>
-  <si>
-    <t>Mar 2021 - Apr 2021</t>
-  </si>
-  <si>
-    <t>This operational research on multi-sectoral nutrition coordination in Ethiopia, supported by UNICEF and the World Bank, assessed coordination mechanisms across various government levels and sectors, identifying bottlenecks and proposing innovative strategies for better nutrition outcomes.</t>
-  </si>
-  <si>
-    <t>conducting nine high-level Key Informant Interviews (KIIs), transcribing, and summarizing the interviews.</t>
-  </si>
-  <si>
-    <t>the qualitative data collected informed the design and establishment of a MSC mechanism for Ethiopia, ensuring lessons learned were addressed across sectors.</t>
-  </si>
-  <si>
-    <t>UNICEF Ethiopia</t>
-  </si>
-  <si>
-    <t>Mesfin Beyero</t>
-  </si>
-  <si>
-    <t>drbeyero@gmail.com</t>
-  </si>
-  <si>
-    <t>Situation Analysis and Baseline Study for EnJOY project</t>
-  </si>
-  <si>
-    <t>ENJOY project baseline</t>
-  </si>
-  <si>
-    <t>Baseline</t>
-  </si>
-  <si>
-    <t>M &amp; E Expert</t>
-  </si>
-  <si>
-    <t>Stata,  Excel</t>
-  </si>
-  <si>
-    <t>Apr 2021 - Jun 2021</t>
-  </si>
-  <si>
-    <t>The EnJOY – (Enhancing Job Opportunities and Employability for Youth and women) project aims to enhance job opportunities for youth and women in Oromia, Sidama, and SNNP regions by improving access to employment information, supporting service delivery, and fostering multi-sectoral collaboration.</t>
-  </si>
-  <si>
-    <t>analyzing and interpreting qualitative and quantitative data (519 survey data points, 80 KIIs, and 40 FGDs) using Stata and Nvivo, populating the project logframe with baseline, and report writeup.</t>
-  </si>
-  <si>
-    <t>supplied project KPIs with baseline data to inform progress along the project logic indicators, identified operational level gaps existing in the job creation space; lack of multisectoral coordination and poor skills training programs identified as learnings, which informed the program and used this feedback to modify its interventions.</t>
-  </si>
-  <si>
-    <t>CARITAS Switzerland</t>
-  </si>
-  <si>
-    <t>European Union</t>
-  </si>
-  <si>
-    <t>Dereje Getu</t>
-  </si>
-  <si>
-    <t>dereje.getu@dabdrt.com</t>
-  </si>
-  <si>
-    <t>Managing director</t>
-  </si>
-  <si>
-    <t>Africa RISING</t>
-  </si>
-  <si>
-    <t>Remote</t>
-  </si>
-  <si>
-    <t>Literature analyst</t>
-  </si>
-  <si>
-    <t>May 2021 - Dec 2021</t>
-  </si>
-  <si>
-    <t>The Africa RISING project aims to enhance smallholder farmers’ livelihoods by increasing productivity, diversifying cropping systems, and mitigating climate risks. It focuses on sustainable intensification, bridging food gaps, and improving crop and livestock integration.</t>
-  </si>
-  <si>
-    <t>responsible for reviewing and synthesizing literature for six potential research articles and developing empirical methodologies to address the associated research question</t>
-  </si>
-  <si>
-    <t>produced and submitted a technical note to the Ministry of Agriculture on the necessary shifts required to improve the livestock market in Ethiopia and produced two research articles</t>
-  </si>
-  <si>
-    <t>ICARDA</t>
-  </si>
-  <si>
-    <t>Girma T. Kassie</t>
-  </si>
-  <si>
-    <t>g.tesfahun@cgiar.org</t>
-  </si>
-  <si>
-    <t>Lead Marketing Economist</t>
-  </si>
-  <si>
-    <t>Systematic literature review</t>
-  </si>
-  <si>
-    <t>Integrated Urban PSNP Baseline Survey</t>
-  </si>
-  <si>
-    <t>UPSNP baseline survey</t>
-  </si>
-  <si>
-    <t>Data quality control expert</t>
-  </si>
-  <si>
-    <t>Apr 2021 - Aug 2021</t>
-  </si>
-  <si>
-    <t>This is a study of the socio-economic conditions of urban Productive Safety Net Program (PSNP) households. The baseline survey used household, health facility, and community surveys to profile beneficiaries of the IUSNP.</t>
-  </si>
-  <si>
-    <t>quality control and managing survey of 4,050 client households, nineteen health centers, and 143 communities using Stata. I provided training for enumerators on three different multi-module questionnaires, monitored data quality and collection progress, and prepared field progress and exit report</t>
-  </si>
-  <si>
-    <t>data collected was used to inform progress of the integrated urban PSNP program, we used the child-focused modules to determine the role of PSNP on children who belonged to the poorest of the poor in Addis Ababa</t>
-  </si>
-  <si>
-    <t>UNICEF Innocenti</t>
-  </si>
-  <si>
-    <t>Kaku Attah Damoah</t>
-  </si>
-  <si>
-    <t>kdamoah@unicef.org</t>
-  </si>
-  <si>
-    <t>Lead researcher</t>
-  </si>
-  <si>
-    <t>Business Analytics</t>
-  </si>
-  <si>
-    <t>Behavioral Insight study survey for household solid waste segregation</t>
-  </si>
-  <si>
-    <t>BI study - waste seggregation</t>
-  </si>
-  <si>
-    <t>Researcher</t>
-  </si>
-  <si>
-    <t>Jun 2021 - Aug 2021</t>
-  </si>
-  <si>
-    <t>The study looked at residential solid waste segregation behavior in Addis Ababa city.</t>
-  </si>
-  <si>
-    <t>designing methodology tool for the behavioral insights study, field survey and data management (1,503 survey data points, twenty-five waste transfer stations, and 3 FGDs) using the Kobo Toolbox, insights report writeup and validation presentation for the client.</t>
-  </si>
-  <si>
-    <t>identified important insights which included type and volume of solid waste of the city, patterns of segregation, moving, landfills, and point of collaboration between the government and private actors to improve waste collection and disposal.</t>
-  </si>
-  <si>
-    <t>Accelerator Lab</t>
-  </si>
-  <si>
-    <t>UNDP Ethiopia</t>
-  </si>
-  <si>
-    <t>Amanuel Tadesse</t>
-  </si>
-  <si>
-    <t>amanuel.tadesse@undp.org</t>
-  </si>
-  <si>
-    <t>Team leader</t>
-  </si>
-  <si>
-    <t>Food Environment Analysis (FEA) – Ethiopia</t>
-  </si>
-  <si>
-    <t>Food Environment Analysis</t>
-  </si>
-  <si>
-    <t>Survey manager</t>
-  </si>
-  <si>
-    <t>Stata,  Excel, ArcGIS</t>
-  </si>
-  <si>
-    <t>Oct 2021 - Dec 2021</t>
-  </si>
-  <si>
-    <t>Nationwide exploratory research of the food environment in Ethiopia using qualitative and quantitative data. The research explored components of the food systems - personal and external domains.</t>
-  </si>
-  <si>
-    <t>analyzing the 2018/19 ESS/LSMS-ISA data to identify food items consumed disaggregated by all major regions and 10 selected representative Woredas (6,670 data points), for selecting Woredas for the qualitative survey based on the food items identified from the quantitative data analysis (19 FGDs, and 81 KIIs), provide training for qualitative research associates, generate map visualization using ArcGIS, verify data quality and participate in the production of a presentation</t>
-  </si>
-  <si>
-    <t>tested the FEA tool of ACDI/VOCA, profiled the food environment in Ethiopia, identified gaps in terms of dietary intakes, food desirability, affordability, accessibility, and nutrition knowledge presented the result to USAID. These gaps warrant introducing project-based interventions to improve the food environment. We made a pitch to USAID.</t>
-  </si>
-  <si>
-    <t>ACDI/VOCA</t>
-  </si>
-  <si>
-    <t>Alysa Grude</t>
-  </si>
-  <si>
-    <t>AGrude@acdivoca.org</t>
-  </si>
-  <si>
-    <t>A Skill Gap Assessment and Identification of Qualification and Occupation</t>
-  </si>
-  <si>
-    <t>Skill gap assessment</t>
+    <t>Impact Evaluation</t>
   </si>
   <si>
     <t>Stata, Kobo, Excel</t>
@@ -490,9 +639,6 @@
     <t>samrawit.getachew@giz.de</t>
   </si>
   <si>
-    <t>M &amp; E specialist</t>
-  </si>
-  <si>
     <t>Young Women and Men's Aspirations and Resilience: Prospects for Livelihoods, Employment and Accountability Before, During and Beyond COVID – 19</t>
   </si>
   <si>
@@ -532,6 +678,12 @@
     <t>WTP study</t>
   </si>
   <si>
+    <t>Environmental Economics</t>
+  </si>
+  <si>
+    <t>Data Cleaning, Management &amp; Integration; Advanced Statistical Analysis &amp; Econometrics; Data Visualization &amp; Reporting; Survey Design, ODK/XLSForms &amp; Data Collection</t>
+  </si>
+  <si>
     <t>Kobo, Stata, Excel</t>
   </si>
   <si>
@@ -556,9 +708,6 @@
     <t>alassefa@gmail.com</t>
   </si>
   <si>
-    <t>Program Director</t>
-  </si>
-  <si>
     <t>Evaluation of the German Financial Co-operation via KfW</t>
   </si>
   <si>
@@ -568,6 +717,12 @@
     <t>Formative Evaluation</t>
   </si>
   <si>
+    <t>Terminal Evaluation</t>
+  </si>
+  <si>
+    <t>Data Cleaning, Management &amp; Integration; Advanced Statistical Analysis &amp; Econometrics; Thematic Qualitative Analysis</t>
+  </si>
+  <si>
     <t>MaxQDA, Stata</t>
   </si>
   <si>
@@ -616,9 +771,6 @@
     <t>selamawitg@psigovet.onmicrosoft.com</t>
   </si>
   <si>
-    <t>Research lead</t>
-  </si>
-  <si>
     <t>Energy Efficiency, Innovation, and Productivity of Enterprises</t>
   </si>
   <si>
@@ -655,6 +807,9 @@
     <t>Ethiopia, The Sudan, South Sudan</t>
   </si>
   <si>
+    <t>Data Cleaning, Management &amp; Integration; Survey Design, ODK/XLSForms &amp; Data Collection</t>
+  </si>
+  <si>
     <t>Kobo, Stata, SPSS</t>
   </si>
   <si>
@@ -685,7 +840,7 @@
     <t>EMERTA final evaluation</t>
   </si>
   <si>
-    <t>Terminal Evaluation</t>
+    <t>Impact Evaluation (Propensity Score Matching, DiD, RCT Calibration); Data Cleaning, Management &amp; Integration; Data Visualization &amp; Reporting</t>
   </si>
   <si>
     <t>Feb 2024 - Apr 2024</t>
@@ -712,9 +867,6 @@
     <t>ydildar@meda.org</t>
   </si>
   <si>
-    <t>Director of impact and knowledge management</t>
-  </si>
-  <si>
     <t>Ethio Legal Shield</t>
   </si>
   <si>
@@ -724,6 +876,9 @@
     <t>Business analyst</t>
   </si>
   <si>
+    <t>Business Analytics &amp; Financial Modeling</t>
+  </si>
+  <si>
     <t>Excel</t>
   </si>
   <si>
@@ -745,9 +900,6 @@
     <t>Tewodros Fikadu</t>
   </si>
   <si>
-    <t>Managing director and founder</t>
-  </si>
-  <si>
     <t>Mobility in a Changing Climate: Strengthening the Capacities of Cities in the Afar and Somali Regions</t>
   </si>
   <si>
@@ -760,306 +912,405 @@
     <t>Migration and climate change expert</t>
   </si>
   <si>
+    <t>Capacity Building</t>
+  </si>
+  <si>
     <t>Stata, R, Python, Excel, QGIS</t>
   </si>
   <si>
-    <t>May 2024 - Jun 2025</t>
+    <t>May 2024 - Aug 2025</t>
+  </si>
+  <si>
+    <t>The project looks at interlinkages of human mobility and climate change, policy, and data gaps in secondary cities in Afar and Somali regional states. It uses research to understand the planning and management of internally displacement of three secondary cities.</t>
+  </si>
+  <si>
+    <t>preparation of inception report, survey design, lead field data collection (quant and qual), data cleaning and management, advanced statistical analysis and visualization using Stata, R, and Python, report writeup.</t>
+  </si>
+  <si>
+    <t>produced a draft analytical report, currently preparing a capacity building training toolbox for local leaders involved in disaster preparedness and response.</t>
+  </si>
+  <si>
+    <t>IOM Ethiopia</t>
+  </si>
+  <si>
+    <t>Kidist Mulugeta</t>
+  </si>
+  <si>
+    <t>kmulugeta@iom.int</t>
+  </si>
+  <si>
+    <t>Tracer Study on Speed School Program: the case of Afar and Somali Regional States</t>
+  </si>
+  <si>
+    <t>Tracer study of SSP</t>
+  </si>
+  <si>
+    <t>Impact Evaluation (Propensity Score Matching, DiD, RCT Calibration); Data Cleaning, Management &amp; Integration; Thematic Qualitative Analysis; Survey Design, ODK/XLSForms &amp; Data Collection</t>
+  </si>
+  <si>
+    <t>Stata, R, Python, MaxQDA, Excel</t>
+  </si>
+  <si>
+    <t>May 2024 - May 2025</t>
+  </si>
+  <si>
+    <t>No link</t>
+  </si>
+  <si>
+    <t>The project is a tracer study of the students enrolled in the Speed School Program – an alternative education program implemented in over six African countries for children that dropped out of primary school, because of climate events and conflict, through an accelerated curriculum. The project is also measures the program’s impact using advanced impact evaluation technique (the Propensity Score Matching).</t>
+  </si>
+  <si>
+    <t>I am the data manager, field supervisor, and assistant researcher to the study lead. In this role, I am responsible for designing the quantitative survey and qualitative field work, drafting data collection tools, design XLSForms, upload the survey forms to the KoboToolbox platform, basic and advanced statistical and econometric analysis of survey data, thematic analysis of qualitative data, and tracer and impact report writeups.</t>
+  </si>
+  <si>
+    <t>drafted inception report of the tracer study; the project is still on going and so far, study tools are developed, translated, and tested for field work.</t>
+  </si>
+  <si>
+    <t>selamawit.kebede@undp.org</t>
+  </si>
+  <si>
+    <t>Business KPIs aggregation and threshold determinantion</t>
+  </si>
+  <si>
+    <t>Constructing aggrgate PM (Remote)</t>
+  </si>
+  <si>
+    <t>Jordan</t>
+  </si>
+  <si>
+    <t>Data Cleaning, Management &amp; Integration; Advanced Statistical Analysis &amp; Econometrics; Business Analytics &amp; Financial Modeling</t>
+  </si>
+  <si>
+    <t>Stata</t>
+  </si>
+  <si>
+    <t>Jan 2025 - Jan 2025</t>
+  </si>
+  <si>
+    <t>Generate comparable performance KPIs for businesses across multiple counries in Europe using Principal Component Analysis.</t>
+  </si>
+  <si>
+    <t>Run the KPI construction, analysis and report writing.</t>
+  </si>
+  <si>
+    <t>Individual</t>
+  </si>
+  <si>
+    <t>Reema Arabel</t>
+  </si>
+  <si>
+    <t>Upwork</t>
+  </si>
+  <si>
+    <t>Develop Input-output Multipliers for Excel</t>
+  </si>
+  <si>
+    <t>Develop IO Multipliers for Excel (Remote)</t>
+  </si>
+  <si>
+    <t>Modelling</t>
+  </si>
+  <si>
+    <t>Saudi Arabia</t>
+  </si>
+  <si>
+    <t>Modeller</t>
+  </si>
+  <si>
+    <t>Data Cleaning, Management &amp; Integration; Advanced Statistical Analysis &amp; Econometrics</t>
+  </si>
+  <si>
+    <t>Excel, GAMS</t>
+  </si>
+  <si>
+    <t>Jan 2025 - Jul 2025</t>
+  </si>
+  <si>
+    <t>Prepare an Excel model for building static and dynamic IO simulation models for the Saudi Arabian economy as represented by its IO data</t>
+  </si>
+  <si>
+    <t>Design, test, and perfect the Excel simulation models</t>
+  </si>
+  <si>
+    <t>Yousef Is</t>
+  </si>
+  <si>
+    <t>Impact Evaluation of Community-Based Training and Disability Inclusion Facilitators Methodology on Governance and Food Security</t>
+  </si>
+  <si>
+    <t>Terminal impact evaluation of CBT and DIF Methodology</t>
+  </si>
+  <si>
+    <t>Impact Evaluation (Propensity Score Matching, DiD, RCT Calibration); Data Cleaning, Management &amp; Integration; Thematic Qualitative Analysis</t>
+  </si>
+  <si>
+    <t>Python, R, Stata, Excel, MaxQDA</t>
+  </si>
+  <si>
+    <t>April 2025 - Aug 2025</t>
+  </si>
+  <si>
+    <t>The evaluation aims to populate the project logframe with terminal values of indicators. It also aims to measure project impact using the using the PSM technique</t>
+  </si>
+  <si>
+    <t>As the evaluation lead, I am responsible for organizing the evaluation team, field work, data quality control, report writing</t>
+  </si>
+  <si>
+    <t>Run reproducible data evaluation analysis and produced a complete evaluation report with two rounds of revisions to include additional client requests</t>
+  </si>
+  <si>
+    <t>TLMIE</t>
+  </si>
+  <si>
+    <t>Natnael Mesfin</t>
+  </si>
+  <si>
+    <t>natnaelm@tlmethiopia.org</t>
+  </si>
+  <si>
+    <t>Accelerating Climate Resilient Food Systems in Ethiopia (ACRFSE): RCT Evaluation Design</t>
+  </si>
+  <si>
+    <t>ACRFSE RCT Evaluation</t>
+  </si>
+  <si>
+    <t>Team member</t>
+  </si>
+  <si>
+    <t>Impact Evaluation (Propensity Score Matching, DiD, RCT Calibration); Data Cleaning, Management &amp; Integration; Data Visualization &amp; Reporting; Survey Design, ODK/XLSForms &amp; Data Collection</t>
+  </si>
+  <si>
+    <t>R, Excel, Stata, Python</t>
+  </si>
+  <si>
+    <t>Aug 2025 - Feb 2026</t>
+  </si>
+  <si>
+    <t>The ACRFSE consortium is formed to strengthen the climate and finance resilience of 10,000 Ethiopian soya bean, teff and maize farmers and their cooperatives to improve their capabilities to cope with increasing climate shocks. The research takes place in Oromia and South Ethiopia regions.</t>
+  </si>
+  <si>
+    <t>Responsible for calibrating the RCT design, data cleaning and management, field work supervision, data analysis using R, study report writing, and production of at least two research articles in peer reviewed journals.</t>
+  </si>
+  <si>
+    <t>Co-designed RCT, managed data cleaning, and initiated two research articles.</t>
+  </si>
+  <si>
+    <t>Policy Studies Institute (PSI)</t>
+  </si>
+  <si>
+    <t>Agriterra</t>
+  </si>
+  <si>
+    <t>Endline Survey Report of the Family MUAC Pilot Study</t>
+  </si>
+  <si>
+    <t>Family MUAC Endline</t>
+  </si>
+  <si>
+    <t>Lead data analyst</t>
+  </si>
+  <si>
+    <t>Stata, Excel, R</t>
+  </si>
+  <si>
+    <t>Dec 2025 - Feb 2026</t>
+  </si>
+  <si>
+    <t>This quasi-experimental/cluster RCT study trained caregivers to measure mid-upper arm circumference (MUAC) and assess edema for early detection of acute malnutrition in children aged 6-47 months in Amhara and Oromia regions. With three arms, the study evaluated training effects on measurement accuracy, self-referral rates, and cost-effectiveness of interventions.</t>
+  </si>
+  <si>
+    <t>Creating data (1,463 caregiver child pairs) cleaning and analysis (including DiD) Stata script (do file). Calculating cost efficiency (using CERs), and disaggregated Cost Effectiveness Analysis (using ICERs) to compare intervention arms.</t>
+  </si>
+  <si>
+    <t>Rewrote data preparation, analysis and generation of result tables and figures in Stata; prepared an end-to-end MS Excel file calculating CERs at different levels of disaggregation, presented the CEA section of the study during the main dissemination workshop with international audience.</t>
+  </si>
+  <si>
+    <t>World Vision US</t>
+  </si>
+  <si>
+    <t>Elazar Tadesse</t>
+  </si>
+  <si>
+    <t>alazar2000@gmail.com</t>
+  </si>
+  <si>
+    <t>A research study on Economic decision making on menstrual health among women and girls in Ethiopian households</t>
+  </si>
+  <si>
+    <t>Menstrual Health Study</t>
+  </si>
+  <si>
+    <t>Overall lead</t>
+  </si>
+  <si>
+    <t>Data Cleaning, Management &amp; Integration; Advanced Statistical Analysis &amp; Econometrics; Survey Design, ODK/XLSForms &amp; Data Collection; Business Analytics &amp; Financial Modeling</t>
+  </si>
+  <si>
+    <t>Survey Solutions, Excel, Stata, Python</t>
+  </si>
+  <si>
+    <t>May 2026 - June 2026</t>
+  </si>
+  <si>
+    <t>No Link</t>
+  </si>
+  <si>
+    <t>This is a comprehensive demand and supply side (supply chain) analysis of the menstrual health products provision to women of reproductive age and adolescent girls in contexts including rural communities, refugees, and people with disabilities. The findings will inform Market Systems Development for a more accessible, affordable, and quality menstrual health products. The research brings together various conceptual frameworks including intra-household dynamics (using collective bargaining models), embedded Willingness to Pay analysis, and conjoint analysis for embedded choice experiments.</t>
+  </si>
+  <si>
+    <t>Overall lead for this assignment. I am responsible for technical deliverables and leadership of the research team.</t>
+  </si>
+  <si>
+    <t>Led research team, designed conjoint analysis experiment.</t>
+  </si>
+  <si>
+    <t>Population Services International (PSI)</t>
+  </si>
+  <si>
+    <t>Michael Negash</t>
+  </si>
+  <si>
+    <t>mnegash@psiet.org</t>
+  </si>
+  <si>
+    <t>Assessment of Multidimensional Poverty in the Southern Ethiopian Region</t>
+  </si>
+  <si>
+    <t>Multidimensional Poverty Assessment</t>
+  </si>
+  <si>
+    <t>Data manager &amp; data analyst</t>
+  </si>
+  <si>
+    <t>Kobo, Excel, Stata, Python</t>
+  </si>
+  <si>
+    <t>May 2026 - July 2026</t>
+  </si>
+  <si>
+    <t>A comprehensive assessing multidimensional poverty across health, education, housing, infrastructure, food security, women's empowerment, and livelihood dimensions using 1,500 household level datapoints. The study generates evidence on socioeconomic, demographic, and geographic characteristics of poverty and the Multi-dimensional Poverty Index (MPI) to inform regional policy and development planning.</t>
+  </si>
+  <si>
+    <t>Responsible for designing the questionnaire in CSPro and XLSForm, quality assurance of data collected using high frequency checks, management and cleaning of data.</t>
+  </si>
+  <si>
+    <t>Designed CSPro questionnaire and established high-frequency data validation check scripts.</t>
+  </si>
+  <si>
+    <t>Wolaita Sodo University (WSU) and South Ethiopia Region Bureau of Planning and Development (SEBPD)</t>
+  </si>
+  <si>
+    <t>South Ethiopia Region Bureau of Planning and Development (SEBPD)</t>
+  </si>
+  <si>
+    <t>Solomon Kebede</t>
+  </si>
+  <si>
+    <t>solomon.kebede@wsu.edu.et</t>
+  </si>
+  <si>
+    <t>The Africa Youth Aspirations and Resilience Survey (AYPReS)</t>
+  </si>
+  <si>
+    <t>AYPReS survey</t>
+  </si>
+  <si>
+    <t>Survey manager &amp; data analyst</t>
+  </si>
+  <si>
+    <t>SurveyCTO, Excel, Stata, R</t>
+  </si>
+  <si>
+    <t>June 2026 - September 2026 (Expected)</t>
   </si>
   <si>
     <t>Ongoing</t>
   </si>
   <si>
-    <t>The project looks at interlinkages of human mobility and climate change, policy, and data gaps in secondary cities in Afar and Somali regional states. It uses research to understand the planning and management of internally displacement of three secondary cities.</t>
-  </si>
-  <si>
-    <t>preparation of inception report, survey design, lead field data collection (quant and qual), data cleaning and management, advanced statistical analysis and visualization using Stata, R, and Python, report writeup.</t>
-  </si>
-  <si>
-    <t>produced a draft analytical report, currently preparing a capacity building training toolbox for local leaders involved in disaster preparedness and response.</t>
-  </si>
-  <si>
-    <t>IOM Ethiopia</t>
-  </si>
-  <si>
-    <t>Kidist Mulugeta</t>
-  </si>
-  <si>
-    <t>kmulugeta@iom.int</t>
-  </si>
-  <si>
-    <t>Tracer Study on Speed School Program: the case of Afar and Somali Regional States</t>
-  </si>
-  <si>
-    <t>Tracer study of SSP</t>
-  </si>
-  <si>
-    <t>Stata, R, Python, MaxQDA, Excel</t>
-  </si>
-  <si>
-    <t>May 2024 - May 2025</t>
-  </si>
-  <si>
-    <t>The project is a tracer study of the students enrolled in the Speed School Program – an alternative education program implemented in over six African countries for children that dropped out of primary school, because of climate events and conflict, through an accelerated curriculum. The project is also measures the program’s impact using advanced impact evaluation technique (the Propensity Score Matching).</t>
-  </si>
-  <si>
-    <t>I am the data manager, field supervisor, and assistant researcher to the study lead. In this role, I am responsible for designing the quantitative survey and qualitative field work, drafting data collection tools, design XLSForms, upload the survey forms to the KoboToolbox platform, basic and advanced statistical and econometric analysis of survey data, thematic analysis of qualitative data, and tracer and impact report writeups.</t>
-  </si>
-  <si>
-    <t>drafted inception report of the tracer study; the project is still on going and so far, study tools are developed, translated, and tested for field work.</t>
-  </si>
-  <si>
-    <t>selamawit.kebede@undp.org</t>
-  </si>
-  <si>
-    <t>Study lead</t>
-  </si>
-  <si>
-    <t>Business KPIs aggregation and threshold determinantion</t>
-  </si>
-  <si>
-    <t>Constructing aggrgate PM (Remote)</t>
-  </si>
-  <si>
-    <t>Jordan</t>
-  </si>
-  <si>
-    <t>Stata</t>
-  </si>
-  <si>
-    <t>Jan 2025 - Jan 2025</t>
-  </si>
-  <si>
-    <t>Generate comparable performance KPIs for businesses across multiple counries in Europe using Principal Component Analysis.</t>
-  </si>
-  <si>
-    <t>Run the KPI construction, analysis and report writing.</t>
-  </si>
-  <si>
-    <t>Individual</t>
-  </si>
-  <si>
-    <t>Reema Arabel</t>
-  </si>
-  <si>
-    <t>Upwork</t>
-  </si>
-  <si>
-    <t>Develop Input-output Multipliers for Excel</t>
-  </si>
-  <si>
-    <t>Develop IO Multipliers for Excel (Remote)</t>
-  </si>
-  <si>
-    <t>Modelling</t>
-  </si>
-  <si>
-    <t>Saudi Arabia</t>
-  </si>
-  <si>
-    <t>Modeller</t>
-  </si>
-  <si>
-    <t>Excel, GAMS</t>
-  </si>
-  <si>
-    <t>Jan 2025 - Jul 2025</t>
-  </si>
-  <si>
-    <t>Prepare an Excel model for building static and dynamic IO simulation models for the Saudi Arabian economy as represented by its IO data</t>
-  </si>
-  <si>
-    <t>Design, test, and perfect the Excel simulation models</t>
-  </si>
-  <si>
-    <t>Yousef Is</t>
-  </si>
-  <si>
-    <t>Impact Evaluation of Community-Based Training and Disability Inclusion Facilitators Methodology on Governance and Food Security</t>
-  </si>
-  <si>
-    <t>Terminal impact evaluation of CBT and DIF Methodology</t>
-  </si>
-  <si>
-    <t>Python, R, Stata, Excel, MaxQDA</t>
-  </si>
-  <si>
-    <t>April 2025 - Aug 2025</t>
-  </si>
-  <si>
-    <t>Accelerating Climate Resilient Food Systems in Ethiopia (ACRFSE): RCT Evaluation Design</t>
-  </si>
-  <si>
-    <t>ACRFSE RCT Evaluation</t>
-  </si>
-  <si>
-    <t>Evaluation</t>
-  </si>
-  <si>
-    <t>Team member</t>
+    <t>Part of a multi-country research initiative by the Partnership for African Social and Governance Research (PASGR) and supported by the Mastercard Foundation. This is a nationally representative sample of 3,382 with the aim to generate robust evidence on youth aspirations, resilience, livelihoods, and system-level dynamics affecting young people aged 15–35 in Ethiopia.</t>
+  </si>
+  <si>
+    <t>Responsible for organizing the quant-qual data field data collection, Survey CTO based tool feedback, data management and cleaning, data quality assurance, and produce field report.</t>
+  </si>
+  <si>
+    <t>Designed the sampling methodology, co-organized field collection framework and prepared SurveyCTO questionnaire form.</t>
+  </si>
+  <si>
+    <t>PASGR (Mastercard foundation funded)</t>
+  </si>
+  <si>
+    <t>Adamnesh Bogale</t>
+  </si>
+  <si>
+    <t>adamne6@yahoo.com</t>
+  </si>
+  <si>
+    <t>id_lng</t>
+  </si>
+  <si>
+    <t>Language</t>
+  </si>
+  <si>
+    <t>Reading</t>
+  </si>
+  <si>
+    <t>Writing</t>
+  </si>
+  <si>
+    <t>Speaking</t>
+  </si>
+  <si>
+    <t>Listening</t>
+  </si>
+  <si>
+    <t>Amharic</t>
+  </si>
+  <si>
+    <t>Native</t>
+  </si>
+  <si>
+    <t>Fluent</t>
+  </si>
+  <si>
+    <t>English</t>
+  </si>
+  <si>
+    <t>Japanese</t>
+  </si>
+  <si>
+    <t>Basic</t>
+  </si>
+  <si>
+    <t>Wolaitigna</t>
+  </si>
+  <si>
+    <t>Intermediate</t>
+  </si>
+  <si>
+    <t>id_sftwr</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Proficiency</t>
+  </si>
+  <si>
+    <t>Python</t>
+  </si>
+  <si>
+    <t>Programming &amp; Data Science</t>
+  </si>
+  <si>
+    <t>Advanced</t>
   </si>
   <si>
     <t>R</t>
   </si>
   <si>
-    <t>Aug 2025 - Feb 2026</t>
-  </si>
-  <si>
-    <t>The ACRFSE consortium is formed to strengthen the climate and finance resilience of 10,000 Ethiopian soya bean, teff and maize farmers and their cooperatives to improve their capabilities to cope with increasing climate shocks. The research takes place in Oromia and South Ethiopia regions.</t>
-  </si>
-  <si>
-    <t>Responsible for calibrating the RCT design, data cleaning and management, field work supervision, data analysis using R, study report writing, and production of at least two research articles in peer reviewed journals.</t>
-  </si>
-  <si>
-    <t>Co-designed RCT, managed data cleaning, and initiated two research articles.</t>
-  </si>
-  <si>
-    <t>Policy Studies Institute (PSI)</t>
-  </si>
-  <si>
-    <t>Endline Survey Report of the Family MUAC Pilot Study</t>
-  </si>
-  <si>
-    <t>Family MUAC Endline</t>
-  </si>
-  <si>
-    <t>Dec 2025 - Feb 2026</t>
-  </si>
-  <si>
-    <t>This quasi-experimental/cluster RCT study trained caregivers to measure mid-upper arm circumference (MUAC) and assess edema for early detection of acute malnutrition in children aged 6-47 months in Amhara and Oromia regions. With three arms, the study evaluated training effects on measurement accuracy, self-referral rates, and cost-effectiveness of interventions.</t>
-  </si>
-  <si>
-    <t>Creating data (1,463 caregiver child pairs) cleaning and analysis (including DiD) Stata script (do file). Calculating cost efficiency (using CERs), and disaggregated Cost Effectiveness Analysis (using ICERs) to compare intervention arms.</t>
-  </si>
-  <si>
-    <t>Rewrote data preparation, analysis and generation of result tables and figures in Stata; prepared an end-to-end MS Excel file calculating CERs at different levels of disaggregation, presented the CEA section of the study during the main dissemination workshop with international audience.</t>
-  </si>
-  <si>
-    <t>World Vision US</t>
-  </si>
-  <si>
-    <t>A research study on Economic decision making on menstrual health among women and girls in Ethiopian households</t>
-  </si>
-  <si>
-    <t>Menstrual Health Study</t>
-  </si>
-  <si>
-    <t>Overall lead</t>
-  </si>
-  <si>
-    <t>This is a comprehensive demand and supply side (supply chain) analysis of the menstrual health products provision to women of reproductive age and adolescent girls in contexts including rural communities, refugees, and people with disabilities. The findings will inform Market Systems Development for a more accessible, affordable, and quality menstrual health products. The research brings together various conceptual frameworks including intra-household dynamics (using collective bargaining models), embedded Willingness to Pay analysis, and conjoint analysis for embedded choice experiments.</t>
-  </si>
-  <si>
-    <t>Overall lead for this assignment. I am responsible for technical deliverables and leadership of the research team.</t>
-  </si>
-  <si>
-    <t>Led research team, designed conjoint analysis experiment.</t>
-  </si>
-  <si>
-    <t>Population Services International (PSI)</t>
-  </si>
-  <si>
-    <t>Assessment of Multidimensional Poverty in the Southern Ethiopian Region</t>
-  </si>
-  <si>
-    <t>Multidimensional Poverty Assessment</t>
-  </si>
-  <si>
-    <t>A comprehensive assessing multidimensional poverty across health, education, housing, infrastructure, food security, women's empowerment, and livelihood dimensions using 1,500 household level datapoints. The study generates evidence on socioeconomic, demographic, and geographic characteristics of poverty and the Multi-dimensional Poverty Index (MPI) to inform regional policy and development planning.</t>
-  </si>
-  <si>
-    <t>Responsible for designing the questionnaire in CSPro and XLSForm, quality assurance of data collected using high frequency checks, management and cleaning of data.</t>
-  </si>
-  <si>
-    <t>Designed CSPro questionnaire and established high-frequency data validation check scripts.</t>
-  </si>
-  <si>
-    <t>Wolaita Sodo University (WSU) and South Ethiopia Region Bureau of Planning and Development (SEBPD)</t>
-  </si>
-  <si>
-    <t>The Africa Youth Aspirations and Resilience Survey (AYPReS)</t>
-  </si>
-  <si>
-    <t>AYPReS survey</t>
-  </si>
-  <si>
-    <t>Survey manager &amp; data analyst</t>
-  </si>
-  <si>
-    <t>June 2026 - September 2026 (Expected)</t>
-  </si>
-  <si>
-    <t>Part of a multi-country research initiative by the Partnership for African Social and Governance Research (PASGR) and supported by the Mastercard Foundation. This is a nationally representative sample of 3,382 with the aim to generate robust evidence on youth aspirations, resilience, livelihoods, and system-level dynamics affecting young people aged 15–35 in Ethiopia.</t>
-  </si>
-  <si>
-    <t>Responsible for organizing the quant-qual data field data collection, Survey CTO based tool feedback, data management and cleaning, data quality assurance, and produce field report.</t>
-  </si>
-  <si>
-    <t>PASGR (Mastercard foundation funded)</t>
-  </si>
-  <si>
-    <t>id_lng</t>
-  </si>
-  <si>
-    <t>Language</t>
-  </si>
-  <si>
-    <t>Reading</t>
-  </si>
-  <si>
-    <t>Writing</t>
-  </si>
-  <si>
-    <t>Speaking</t>
-  </si>
-  <si>
-    <t>Listening</t>
-  </si>
-  <si>
-    <t>Amharic</t>
-  </si>
-  <si>
-    <t>Native</t>
-  </si>
-  <si>
-    <t>Fluent</t>
-  </si>
-  <si>
-    <t>English</t>
-  </si>
-  <si>
-    <t>Japanese</t>
-  </si>
-  <si>
-    <t>Basic</t>
-  </si>
-  <si>
-    <t>Wolaitigna</t>
-  </si>
-  <si>
-    <t>Intermediate</t>
-  </si>
-  <si>
-    <t>id_sftwr</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Category</t>
-  </si>
-  <si>
-    <t>Proficiency</t>
-  </si>
-  <si>
-    <t>Python</t>
-  </si>
-  <si>
-    <t>Programming &amp; Data Science</t>
-  </si>
-  <si>
-    <t>Advanced</t>
-  </si>
-  <si>
     <t>Statistical Analysis</t>
   </si>
   <si>
@@ -1120,6 +1371,33 @@
     <t>CSPro</t>
   </si>
   <si>
+    <t>ODK</t>
+  </si>
+  <si>
+    <t>Qualtrics</t>
+  </si>
+  <si>
+    <t>RedCAP</t>
+  </si>
+  <si>
+    <t>LaTeX</t>
+  </si>
+  <si>
+    <t>Typesetting &amp; Markup</t>
+  </si>
+  <si>
+    <t>RMarkdown</t>
+  </si>
+  <si>
+    <t>Quarto</t>
+  </si>
+  <si>
+    <t>Microsoft Office 365</t>
+  </si>
+  <si>
+    <t>Office Productivity</t>
+  </si>
+  <si>
     <t>id_skll</t>
   </si>
   <si>
@@ -1150,9 +1428,6 @@
     <t>Survey Design, ODK/XLSForms &amp; Data Collection</t>
   </si>
   <si>
-    <t>Business Analytics &amp; Financial Modeling</t>
-  </si>
-  <si>
     <t>Academic Instruction &amp; Thesis Supervision</t>
   </si>
   <si>
@@ -1378,229 +1653,46 @@
     <t>Taught classes for undergraduate students.</t>
   </si>
   <si>
-    <t>id_pub</t>
-  </si>
-  <si>
-    <t>Citation</t>
-  </si>
-  <si>
-    <t>Year</t>
-  </si>
-  <si>
-    <t>Publisher/Journal</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>Desalegn, Y. (2020). Off-farm Activities, Incomes and Household Welfare in Rural Ethiopia. Addis Ababa University and JIBS, Ethiopia under the supervision of Almas Heshmati (PhD), Jonkoping International Business School (JIBS), Jonkoping University, Sweden, and Adane Tufa (PhD), Department of Economics, Addis Ababa University (AAU), Ethiopia</t>
-  </si>
-  <si>
-    <t>Off-farm Activities, Incomes and Household Welfare in Rural Ethiopia</t>
-  </si>
-  <si>
-    <t>Addis Ababa University &amp; Jönköping University (Dissertation)</t>
-  </si>
-  <si>
-    <t>PhD Dissertation</t>
-  </si>
-  <si>
-    <t>Desalegn, Y. (2018). Returns to education in Ethiopia. In Economic Growth and Development in Ethiopia (pp. 199-226). Springer, Singapore.</t>
-  </si>
-  <si>
-    <t>Returns to education in Ethiopia</t>
-  </si>
-  <si>
-    <t>Springer, Singapore (Book Chapter)</t>
-  </si>
-  <si>
-    <t>Book Chapter</t>
-  </si>
-  <si>
-    <t>Tegegn, T., Paulos, M., &amp; Desalegn, Y. (2016). Determinants of Entrepreneurial Intention among Prospective Graduates of Higher Institutions Case of Wolaita Sodo University. Journal of Education and Practice, 7(16), 46-53.</t>
-  </si>
-  <si>
-    <t>Determinants of Entrepreneurial Intention among Prospective Graduates of Higher Institutions Case of Wolaita Sodo University</t>
-  </si>
-  <si>
-    <t>Journal of Education and Practice</t>
-  </si>
-  <si>
-    <t>Journal Article</t>
-  </si>
-  <si>
-    <t>Amphune, B. E., Weldegebriel, Z. B., &amp; Enaro, Y. D. (2018). Migration and Urban Livelihoods: A Quest for Sustainability in Southern Ethiopia.</t>
-  </si>
-  <si>
-    <t>Migration and Urban Livelihoods: A Quest for Sustainability in Southern Ethiopia</t>
-  </si>
-  <si>
-    <t>Unpublished/Other</t>
-  </si>
-  <si>
-    <t>Kassie, G.T., Y. Desalegn, W. Asnake, A. Haile, and B. Rischkowsky. (2021). Synthesis report on critical challenges and necessary strategic shifts in livestock market development in Ethiopia. Working Paper. ICARDA (International Center for Agricultural Research in the Dry Areas). Beirut, Lebanon.</t>
-  </si>
-  <si>
-    <t>Synthesis report on critical challenges and necessary strategic shifts in livestock market development in Ethiopia</t>
-  </si>
-  <si>
-    <t>ICARDA Working Paper</t>
-  </si>
-  <si>
-    <t>Working Paper</t>
-  </si>
-  <si>
-    <t>Girma Kassie, Aynalem Haile, Woinishet Asnake, Yonatan Desalegn, Barbara Rischkowsky. (2021). Impact of Community-based breeding program on the performance of and income from small ruminants in Ethiopia. Working Paper. CGIAR-ICARDA.</t>
-  </si>
-  <si>
-    <t>Impact of Community-based breeding program on the performance of and income from small ruminants in Ethiopia</t>
-  </si>
-  <si>
-    <t>CGIAR-ICARDA Working Paper</t>
-  </si>
-  <si>
     <t>id_data</t>
   </si>
   <si>
     <t>Dataset name</t>
   </si>
   <si>
+    <t>Short name</t>
+  </si>
+  <si>
     <t>Source</t>
   </si>
   <si>
-    <t>Lead data analyst</t>
-  </si>
-  <si>
-    <t>Data manager &amp; data analyst</t>
-  </si>
-  <si>
-    <t>Kobo, Excel, Stata, Python</t>
-  </si>
-  <si>
-    <t>R, Excel, Stata, Python</t>
-  </si>
-  <si>
-    <t>May 2026 - July 2026</t>
-  </si>
-  <si>
-    <t>May 2026 - June 2026</t>
-  </si>
-  <si>
-    <t>Survey Solutions, Excel, Stata, Python</t>
-  </si>
-  <si>
-    <t>SurveyCTO, Excel, Stata, R</t>
-  </si>
-  <si>
-    <t>Stata, Excel, R</t>
-  </si>
-  <si>
-    <t>Most Significant Change (MSC)</t>
-  </si>
-  <si>
-    <t>No link</t>
-  </si>
-  <si>
-    <t>No Link</t>
-  </si>
-  <si>
-    <t>Michael Negash</t>
-  </si>
-  <si>
-    <t>mnegash@psiet.org</t>
-  </si>
-  <si>
-    <t>Designed the sampling methodology, co-organized field collection framework and prepared SurveyCTO questionnaire form.</t>
-  </si>
-  <si>
-    <t>South Ethiopia Region Bureau of Planning and Development (SEBPD)</t>
-  </si>
-  <si>
-    <t>Agriterra</t>
-  </si>
-  <si>
-    <t>TLMIE</t>
-  </si>
-  <si>
-    <t>ZOA</t>
-  </si>
-  <si>
-    <t>Natnael Mesfin</t>
-  </si>
-  <si>
-    <t>natnaelm@tlmethiopia.org</t>
-  </si>
-  <si>
-    <t>The evaluation aims to populate the project logframe with terminal values of indicators. It also aims to measure project impact using the using the PSM technique</t>
-  </si>
-  <si>
-    <t>As the evaluation lead, I am responsible for organizing the evaluation team, field work, data quality control, report writing</t>
-  </si>
-  <si>
-    <t>Run reproducible data evaluation analysis and produced a complete evaluation report with two rounds of revisions to include additional client requests</t>
-  </si>
-  <si>
-    <t>Freelance client</t>
-  </si>
-  <si>
-    <t>Reseach lead</t>
-  </si>
-  <si>
-    <t>alazar2000@gmail.com</t>
-  </si>
-  <si>
-    <t>Elazar Tadesse</t>
-  </si>
-  <si>
-    <t>Solomon Kebede</t>
-  </si>
-  <si>
-    <t>solomon.kebede@wsu.edu.et</t>
-  </si>
-  <si>
-    <t>Adamnesh Bogale</t>
-  </si>
-  <si>
-    <t>adamne6@yahoo.com</t>
-  </si>
-  <si>
-    <t>GitHub rep</t>
-  </si>
-  <si>
-    <t>Empowering Caregivers to Assess and Evaluate Child Nutrition Outcomes: A Pilot Study from Rural Ethiopia</t>
-  </si>
-  <si>
-    <t>Ninth International CREA Conference</t>
-  </si>
-  <si>
-    <t>Conference paper</t>
-  </si>
-  <si>
-    <t>Mamo, Tigist; Tadesse, Elazar; Oranga, Beryl; Desalegn, Yonatan; Tumusiime, Emmanuel; Kirby, Miles; Reider, Kathryn; Wagg, Michael. (2026). Empowering Caregivers to Assess and Evaluate Child Nutrition Outcomes: A Pilot Study from Rural Ethiopia. Working paper. Ninth International CREA Conference</t>
-  </si>
-  <si>
-    <t>Impact of Family MUAC Training and Supervision Intensity on Caregivers Accuracy and Cost‑Effectiveness in Rural Ethiopia</t>
-  </si>
-  <si>
-    <t>Nutrition 2026 conference of American Society of Nutrition</t>
-  </si>
-  <si>
-    <t>Tigist M.Cherkos, Elazar T. Balla, Yonatan D.Enaro, Miles Kirby, Precious M. Mubanga, Beryl A. Oranga, Kathryn Reider, Emmanuel Tumusiime. (2026). Impact of Family MUAC Training and Supervision Intensity on Caregivers Accuracy and Cost‑Effectiveness in Rural Ethiopia. Conference paper. Nutrition 2026</t>
+    <t>Data type</t>
   </si>
   <si>
     <t>Young Lives</t>
   </si>
   <si>
+    <t>YL</t>
+  </si>
+  <si>
     <t>UK data service</t>
   </si>
   <si>
-    <t>Child labor and schooling outcomes -  a cross continent analysis</t>
-  </si>
-  <si>
-    <t>Yonatan Desalegn and Tamrate Woldemariam. (2026) Child labor and schooling outcomes -  a cross continent analysis. Forthcoming</t>
-  </si>
-  <si>
-    <t>Research manuscript</t>
+    <t>Panel</t>
+  </si>
+  <si>
+    <t>A unique longitudinal cohort study tracking childhood poverty, education, and health outcomes over multiple decades.</t>
+  </si>
+  <si>
+    <t>Ethiopian Rural Households Survey</t>
+  </si>
+  <si>
+    <t>ERHS</t>
+  </si>
+  <si>
+    <t>AAU, IFPRI, and University of Oxford</t>
+  </si>
+  <si>
+    <t>The Ethiopian Rural Household Survey (ERHS) is a unique, longitudinally rich dataset specifically designed to monitor rural livelihoods, agricultural practices, and socioeconomic changes across multiple decades.</t>
   </si>
   <si>
     <t>LSMS-ISA</t>
@@ -1609,88 +1701,103 @@
     <t>World bank and Ethiopian Statistical Services</t>
   </si>
   <si>
+    <t>High-quality, multi-topic household panel survey with a strong focus on agricultural productivity, land use, and rural livelihoods.</t>
+  </si>
+  <si>
+    <t>World Bank Enterprise Survey</t>
+  </si>
+  <si>
     <t>WBES</t>
   </si>
   <si>
+    <t>Repeated cross sectional</t>
+  </si>
+  <si>
+    <t>Firm-level survey monitoring the business environment, productivity, operational constraints, and growth of formal enterprises.</t>
+  </si>
+  <si>
     <t>National Labor Force Survey</t>
   </si>
   <si>
+    <t>NLFS</t>
+  </si>
+  <si>
+    <t>Ethiopian Statistical Services</t>
+  </si>
+  <si>
+    <t>Nationwide survey capturing employment dynamics, unemployment rates, underemployment, and formal/informal labor market characteristics.</t>
+  </si>
+  <si>
     <t>Agricultural Sample Survey</t>
   </si>
   <si>
-    <t>Short name</t>
-  </si>
-  <si>
-    <t>YL</t>
-  </si>
-  <si>
-    <t>NLFS</t>
-  </si>
-  <si>
-    <t>World Bank Enterprise Survey</t>
-  </si>
-  <si>
     <t>AgSS</t>
   </si>
   <si>
+    <t>Annual comprehensive assessment providing critical estimates on crop acreage, yield forecasts, livestock populations, and agricultural inputs.</t>
+  </si>
+  <si>
+    <t>Household Consumption and Expenditure Survey</t>
+  </si>
+  <si>
     <t>HCES</t>
   </si>
   <si>
-    <t>Household Consumption and Expenditure Survey</t>
-  </si>
-  <si>
-    <t>Ethiopian Statistical Services</t>
+    <t>Major household survey used to calculate poverty lines, assess consumption patterns, and estimate national nutritional welfare indicators.</t>
   </si>
   <si>
     <t>Proprietory data</t>
   </si>
   <si>
-    <t>A unique longitudinal cohort study tracking childhood poverty, education, and health outcomes over multiple decades.</t>
-  </si>
-  <si>
-    <t>High-quality, multi-topic household panel survey with a strong focus on agricultural productivity, land use, and rural livelihoods.</t>
-  </si>
-  <si>
-    <t>Firm-level survey monitoring the business environment, productivity, operational constraints, and growth of formal enterprises.</t>
-  </si>
-  <si>
-    <t>Nationwide survey capturing employment dynamics, unemployment rates, underemployment, and formal/informal labor market characteristics.</t>
-  </si>
-  <si>
-    <t>Annual comprehensive assessment providing critical estimates on crop acreage, yield forecasts, livestock populations, and agricultural inputs.</t>
-  </si>
-  <si>
-    <t>Major household survey used to calculate poverty lines, assess consumption patterns, and estimate national nutritional welfare indicators.</t>
+    <t>Various</t>
+  </si>
+  <si>
+    <t>Mixed</t>
   </si>
   <si>
     <t>Custom, primary research datasets collected for specific client evaluations, localized project baselines, or targeted institutional studies.</t>
   </si>
   <si>
-    <t>ERHS</t>
-  </si>
-  <si>
-    <t>Ethiopian Rural Households Survey</t>
-  </si>
-  <si>
-    <t>The Ethiopian Rural Household Survey (ERHS) is a unique, longitudinally rich dataset specifically designed to monitor rural livelihoods, agricultural practices, and socioeconomic changes across multiple decades.</t>
-  </si>
-  <si>
-    <t>Data type</t>
-  </si>
-  <si>
-    <t>Panel</t>
-  </si>
-  <si>
-    <t>Repeated cross sectional</t>
-  </si>
-  <si>
-    <t>Mixed</t>
-  </si>
-  <si>
-    <t>Various</t>
-  </si>
-  <si>
-    <t>AAU, IFPRI, and University of Oxford</t>
+    <t>id_pt</t>
+  </si>
+  <si>
+    <t>Role type</t>
+  </si>
+  <si>
+    <t>Position</t>
+  </si>
+  <si>
+    <t>Editorial</t>
+  </si>
+  <si>
+    <t>Associate Editor</t>
+  </si>
+  <si>
+    <t>Journal of Science and Inclusive Development (Wolaita Sodo University)</t>
+  </si>
+  <si>
+    <t>Sep 2021 - Present</t>
+  </si>
+  <si>
+    <t>Screening and reviewing manuscript submissions for the journal under the thematic areas of business and economics.</t>
+  </si>
+  <si>
+    <t>Reviewer</t>
+  </si>
+  <si>
+    <t>Journal article reviewer</t>
+  </si>
+  <si>
+    <t>Eastern Africa Social Science Research Review (EASSRR)</t>
+  </si>
+  <si>
+    <t>Peer review of journal articles.</t>
+  </si>
+  <si>
+    <t>id_exp</t>
+  </si>
+  <si>
+    <t>Expertise</t>
   </si>
 </sst>
 </file>
@@ -1733,9 +1840,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1749,6 +1856,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1765,10 +1873,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2056,7 +2160,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AR28"/>
+  <dimension ref="A1:AQ28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="2" bestFit="1" customWidth="1"/>
@@ -2065,193 +2169,197 @@
     <col min="4" max="4" width="25.28515625" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="31.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.140625" style="2"/>
+    <col min="7" max="7" width="9.140625" style="2" customWidth="1"/>
     <col min="8" max="8" width="34.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="9.140625" style="2"/>
+    <col min="9" max="10" width="9.140625" style="2" customWidth="1"/>
     <col min="11" max="11" width="34.85546875" style="2" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="36.28515625" style="2" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="17.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="22" width="9.140625" style="2"/>
+    <col min="14" max="22" width="9.140625" style="2" customWidth="1"/>
     <col min="23" max="23" width="11.5703125" style="2" customWidth="1"/>
-    <col min="24" max="42" width="9.140625" style="2"/>
+    <col min="24" max="42" width="9.140625" style="2" customWidth="1"/>
     <col min="43" max="43" width="44.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="44" max="44" width="26.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="45" max="16384" width="9.140625" style="2"/>
+    <col min="45" max="45" width="9.140625" style="2" customWidth="1"/>
+    <col min="46" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44" s="3" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:43" s="3" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>6</v>
+        <v>43</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>10</v>
+        <v>47</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="R1" s="3" t="s">
-        <v>17</v>
+        <v>54</v>
       </c>
       <c r="S1" s="3" t="s">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="T1" s="3" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="U1" s="3" t="s">
-        <v>20</v>
+        <v>57</v>
       </c>
       <c r="V1" s="3" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="W1" s="3" t="s">
-        <v>488</v>
+        <v>59</v>
       </c>
       <c r="X1" s="3" t="s">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="Y1" s="3" t="s">
-        <v>23</v>
+        <v>61</v>
       </c>
       <c r="Z1" s="3" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="AA1" s="3" t="s">
-        <v>25</v>
+        <v>63</v>
       </c>
       <c r="AB1" s="3" t="s">
-        <v>26</v>
+        <v>64</v>
       </c>
       <c r="AC1" s="3" t="s">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="AD1" s="3" t="s">
-        <v>511</v>
+        <v>66</v>
       </c>
       <c r="AE1" s="3" t="s">
-        <v>28</v>
+        <v>67</v>
       </c>
       <c r="AF1" s="3" t="s">
-        <v>29</v>
+        <v>68</v>
       </c>
       <c r="AG1" s="3" t="s">
-        <v>30</v>
+        <v>69</v>
       </c>
       <c r="AH1" s="3" t="s">
-        <v>31</v>
+        <v>70</v>
       </c>
       <c r="AI1" s="3" t="s">
-        <v>32</v>
+        <v>71</v>
       </c>
       <c r="AJ1" s="3" t="s">
-        <v>33</v>
+        <v>72</v>
       </c>
       <c r="AK1" s="3" t="s">
-        <v>34</v>
+        <v>73</v>
       </c>
       <c r="AL1" s="3" t="s">
-        <v>35</v>
+        <v>74</v>
       </c>
       <c r="AM1" s="3" t="s">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="AN1" s="3" t="s">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="AO1" s="3" t="s">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="AP1" s="3" t="s">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="AQ1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="AR1" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="2" spans="1:44" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="2" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>41</v>
+        <v>80</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>43</v>
+        <v>82</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>44</v>
+        <v>83</v>
       </c>
       <c r="F2" s="2">
         <v>9</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>45</v>
+        <v>84</v>
+      </c>
+      <c r="I2" t="s">
+        <v>85</v>
+      </c>
+      <c r="J2" t="s">
+        <v>86</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>46</v>
+        <v>87</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>47</v>
+        <v>88</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>48</v>
+        <v>89</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="Q2" s="2">
         <v>149</v>
@@ -2260,200 +2368,200 @@
         <v>1</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="T2" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="V2" s="2">
         <v>4</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>51</v>
+        <v>92</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="AE2" s="2">
         <v>114</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="AG2" s="2">
         <v>24</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="AI2" s="2">
         <v>0</v>
       </c>
       <c r="AJ2" s="2" t="s">
-        <v>52</v>
+        <v>93</v>
       </c>
       <c r="AK2" s="2" t="s">
-        <v>53</v>
+        <v>94</v>
       </c>
       <c r="AL2" s="2" t="s">
-        <v>54</v>
+        <v>95</v>
       </c>
       <c r="AM2" s="2" t="s">
-        <v>55</v>
+        <v>96</v>
       </c>
       <c r="AN2" s="2" t="s">
-        <v>56</v>
+        <v>97</v>
       </c>
       <c r="AO2" s="2" t="s">
-        <v>57</v>
+        <v>98</v>
       </c>
       <c r="AP2" s="2" t="s">
-        <v>58</v>
+        <v>99</v>
       </c>
       <c r="AQ2" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="AR2" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="3" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>61</v>
+        <v>101</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>62</v>
+        <v>102</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>43</v>
+        <v>82</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>44</v>
+        <v>83</v>
       </c>
       <c r="F3" s="2">
         <v>1</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>63</v>
+        <v>103</v>
+      </c>
+      <c r="I3" t="s">
+        <v>85</v>
+      </c>
+      <c r="J3" t="s">
+        <v>104</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>64</v>
+        <v>105</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>48</v>
+        <v>89</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="T3" s="2">
         <v>9</v>
       </c>
       <c r="U3" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="W3" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="X3" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="Y3" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="Z3" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="AA3" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="AB3" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="AD3" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="AF3" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="AH3" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="AI3" s="2">
         <v>0</v>
       </c>
       <c r="AJ3" s="2" t="s">
-        <v>65</v>
+        <v>106</v>
       </c>
       <c r="AK3" s="2" t="s">
-        <v>66</v>
+        <v>107</v>
       </c>
       <c r="AL3" s="2" t="s">
-        <v>67</v>
+        <v>108</v>
       </c>
       <c r="AM3" s="2" t="s">
-        <v>68</v>
+        <v>109</v>
       </c>
       <c r="AN3" s="2" t="s">
-        <v>68</v>
+        <v>109</v>
       </c>
       <c r="AO3" s="2" t="s">
-        <v>69</v>
+        <v>110</v>
       </c>
       <c r="AP3" s="2" t="s">
-        <v>70</v>
+        <v>111</v>
       </c>
       <c r="AQ3" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="AR3" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="4" spans="1:44" x14ac:dyDescent="0.25">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="4" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>71</v>
+        <v>112</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>72</v>
+        <v>113</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>73</v>
+        <v>114</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>44</v>
+        <v>83</v>
       </c>
       <c r="F4" s="2">
         <v>3</v>
@@ -2462,25 +2570,31 @@
         <v>8</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>74</v>
+        <v>115</v>
+      </c>
+      <c r="I4" t="s">
+        <v>116</v>
+      </c>
+      <c r="J4" t="s">
+        <v>117</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>75</v>
+        <v>118</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>76</v>
+        <v>119</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>48</v>
+        <v>89</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="Q4" s="2">
         <v>519</v>
@@ -2489,194 +2603,194 @@
         <v>1</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="T4" s="2">
         <v>80</v>
       </c>
       <c r="U4" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="V4" s="2">
         <v>40</v>
       </c>
       <c r="W4" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="X4" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="Y4" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="Z4" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="AA4" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="AB4" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="AD4" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="AE4" s="2">
         <v>105</v>
       </c>
       <c r="AF4" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="AH4" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="AI4" s="2">
         <v>20</v>
       </c>
       <c r="AJ4" s="2" t="s">
-        <v>77</v>
+        <v>120</v>
       </c>
       <c r="AK4" s="2" t="s">
-        <v>78</v>
+        <v>121</v>
       </c>
       <c r="AL4" s="2" t="s">
-        <v>79</v>
+        <v>122</v>
       </c>
       <c r="AM4" s="2" t="s">
-        <v>80</v>
+        <v>123</v>
       </c>
       <c r="AN4" s="2" t="s">
-        <v>81</v>
+        <v>124</v>
       </c>
       <c r="AO4" s="2" t="s">
-        <v>82</v>
+        <v>125</v>
       </c>
       <c r="AP4" s="2" t="s">
-        <v>83</v>
+        <v>126</v>
       </c>
       <c r="AQ4" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="AR4" s="2" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="5" spans="1:44" x14ac:dyDescent="0.25">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="5" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>85</v>
+        <v>128</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>85</v>
+        <v>128</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>25</v>
+        <v>63</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>86</v>
+        <v>129</v>
       </c>
       <c r="F5" s="2">
         <v>1</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>87</v>
+        <v>130</v>
+      </c>
+      <c r="I5" t="s">
+        <v>131</v>
+      </c>
+      <c r="J5" t="s">
+        <v>132</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>88</v>
+        <v>133</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>48</v>
+        <v>89</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="S5" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="U5" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="W5" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="X5" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="Y5" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="Z5" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="AA5" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="AB5" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="AD5" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="AE5" s="2">
         <v>180</v>
       </c>
       <c r="AF5" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="AH5" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="AI5" s="2">
         <v>0</v>
       </c>
       <c r="AJ5" s="2" t="s">
-        <v>89</v>
+        <v>134</v>
       </c>
       <c r="AK5" s="2" t="s">
-        <v>90</v>
+        <v>135</v>
       </c>
       <c r="AL5" s="2" t="s">
-        <v>91</v>
+        <v>136</v>
       </c>
       <c r="AM5" s="2" t="s">
-        <v>92</v>
+        <v>137</v>
       </c>
       <c r="AO5" s="2" t="s">
-        <v>93</v>
+        <v>138</v>
       </c>
       <c r="AP5" s="2" t="s">
-        <v>94</v>
+        <v>139</v>
       </c>
       <c r="AQ5" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="AR5" s="2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="6" spans="1:44" x14ac:dyDescent="0.25">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="6" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>97</v>
+        <v>141</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>98</v>
+        <v>142</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>73</v>
+        <v>114</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>44</v>
+        <v>83</v>
       </c>
       <c r="F6" s="2">
         <v>1</v>
@@ -2685,111 +2799,114 @@
         <v>32</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>99</v>
+        <v>143</v>
+      </c>
+      <c r="I6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J6" t="s">
+        <v>145</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>75</v>
+        <v>118</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>100</v>
+        <v>146</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>48</v>
+        <v>89</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="Q6" s="2">
-        <v>4212</v>
+        <v>4050</v>
       </c>
       <c r="R6" s="2">
         <v>3</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="U6" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="W6" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="X6" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="Y6" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="Z6" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="AA6" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="AB6" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="AD6" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="AF6" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="AH6" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="AI6" s="2">
         <v>30</v>
       </c>
       <c r="AJ6" s="2" t="s">
-        <v>101</v>
+        <v>147</v>
       </c>
       <c r="AK6" s="2" t="s">
-        <v>102</v>
+        <v>148</v>
       </c>
       <c r="AL6" s="2" t="s">
-        <v>103</v>
+        <v>149</v>
       </c>
       <c r="AM6" s="2" t="s">
-        <v>104</v>
+        <v>150</v>
       </c>
       <c r="AN6" s="2" t="s">
-        <v>68</v>
+        <v>109</v>
       </c>
       <c r="AO6" s="2" t="s">
-        <v>105</v>
+        <v>151</v>
       </c>
       <c r="AP6" s="2" t="s">
-        <v>106</v>
+        <v>152</v>
       </c>
       <c r="AQ6" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="AR6" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="7" spans="1:44" x14ac:dyDescent="0.25">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="7" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>109</v>
+        <v>154</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>110</v>
+        <v>155</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>44</v>
+        <v>83</v>
       </c>
       <c r="F7" s="2">
         <v>1</v>
@@ -2798,120 +2915,123 @@
         <v>14</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>111</v>
+        <v>156</v>
+      </c>
+      <c r="I7" t="s">
+        <v>85</v>
+      </c>
+      <c r="J7" t="s">
+        <v>157</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>46</v>
+        <v>87</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>112</v>
+        <v>158</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>48</v>
+        <v>89</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="Q7" s="2">
-        <v>1528</v>
+        <v>1503</v>
       </c>
       <c r="R7" s="2">
         <v>2</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="U7" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="V7" s="2">
         <v>3</v>
       </c>
       <c r="W7" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="X7" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="Y7" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="Z7" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="AA7" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="AB7" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="AD7" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="AE7" s="2">
         <v>54</v>
       </c>
       <c r="AF7" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="AG7" s="2">
         <v>40</v>
       </c>
       <c r="AH7" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="AI7" s="2">
         <v>15</v>
       </c>
       <c r="AJ7" s="2" t="s">
-        <v>113</v>
+        <v>159</v>
       </c>
       <c r="AK7" s="2" t="s">
-        <v>114</v>
+        <v>160</v>
       </c>
       <c r="AL7" s="2" t="s">
-        <v>115</v>
+        <v>161</v>
       </c>
       <c r="AM7" s="2" t="s">
-        <v>116</v>
+        <v>162</v>
       </c>
       <c r="AN7" s="2" t="s">
-        <v>117</v>
+        <v>163</v>
       </c>
       <c r="AO7" s="2" t="s">
-        <v>118</v>
+        <v>164</v>
       </c>
       <c r="AP7" s="2" t="s">
-        <v>119</v>
+        <v>165</v>
       </c>
       <c r="AQ7" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="AR7" s="2" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="8" spans="1:44" x14ac:dyDescent="0.25">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="8" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>121</v>
+        <v>166</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>122</v>
+        <v>167</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>44</v>
+        <v>83</v>
       </c>
       <c r="F8" s="2">
         <v>5</v>
@@ -2920,120 +3040,123 @@
         <v>10</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>123</v>
+        <v>168</v>
+      </c>
+      <c r="I8" t="s">
+        <v>116</v>
+      </c>
+      <c r="J8" t="s">
+        <v>169</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>124</v>
+        <v>170</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>125</v>
+        <v>171</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>48</v>
+        <v>89</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="Q8" s="2">
-        <v>10</v>
+        <v>6670</v>
       </c>
       <c r="R8" s="2">
         <v>1</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="T8" s="2">
         <v>81</v>
       </c>
       <c r="U8" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="V8" s="2">
         <v>19</v>
       </c>
       <c r="W8" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="X8" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="Y8" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="Z8" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="AA8" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="AB8" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="AD8" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="AF8" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="AG8" s="2">
         <v>20</v>
       </c>
       <c r="AH8" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="AI8" s="2">
         <v>10</v>
       </c>
       <c r="AJ8" s="2" t="s">
-        <v>126</v>
+        <v>172</v>
       </c>
       <c r="AK8" s="2" t="s">
-        <v>127</v>
+        <v>173</v>
       </c>
       <c r="AL8" s="2" t="s">
-        <v>128</v>
+        <v>174</v>
       </c>
       <c r="AM8" s="2" t="s">
-        <v>129</v>
+        <v>175</v>
       </c>
       <c r="AN8" s="2" t="s">
-        <v>129</v>
+        <v>175</v>
       </c>
       <c r="AO8" s="2" t="s">
-        <v>130</v>
+        <v>176</v>
       </c>
       <c r="AP8" s="2" t="s">
-        <v>131</v>
+        <v>177</v>
       </c>
       <c r="AQ8" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="AR8" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="9" spans="1:44" x14ac:dyDescent="0.25">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="9" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>132</v>
+        <v>178</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>43</v>
+        <v>82</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>44</v>
+        <v>83</v>
       </c>
       <c r="F9" s="2">
         <v>1</v>
@@ -3042,25 +3165,31 @@
         <v>4</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>59</v>
+        <v>180</v>
+      </c>
+      <c r="I9" t="s">
+        <v>181</v>
+      </c>
+      <c r="J9" t="s">
+        <v>145</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>134</v>
+        <v>182</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>135</v>
+        <v>183</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>48</v>
+        <v>89</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="Q9" s="2">
         <v>369</v>
@@ -3069,93 +3198,90 @@
         <v>6</v>
       </c>
       <c r="S9" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="T9" s="2">
         <v>19</v>
       </c>
       <c r="U9" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="V9" s="2">
         <v>8</v>
       </c>
       <c r="W9" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="X9" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="Y9" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="Z9" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="AA9" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="AB9" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="AE9" s="2">
         <v>119</v>
       </c>
       <c r="AF9" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="AG9" s="2">
         <v>49</v>
       </c>
       <c r="AH9" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="AI9" s="2">
         <v>25</v>
       </c>
       <c r="AJ9" s="2" t="s">
-        <v>136</v>
+        <v>184</v>
       </c>
       <c r="AK9" s="2" t="s">
-        <v>137</v>
+        <v>185</v>
       </c>
       <c r="AL9" s="2" t="s">
-        <v>138</v>
+        <v>186</v>
       </c>
       <c r="AM9" s="2" t="s">
-        <v>139</v>
+        <v>187</v>
       </c>
       <c r="AN9" s="2" t="s">
-        <v>140</v>
+        <v>188</v>
       </c>
       <c r="AO9" s="2" t="s">
-        <v>82</v>
+        <v>125</v>
       </c>
       <c r="AP9" s="2" t="s">
-        <v>83</v>
+        <v>126</v>
       </c>
       <c r="AQ9" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="AR9" s="2" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="10" spans="1:44" x14ac:dyDescent="0.25">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="10" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>142</v>
+        <v>190</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>143</v>
+        <v>191</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>144</v>
+        <v>192</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>44</v>
+        <v>83</v>
       </c>
       <c r="F10" s="2">
         <v>2</v>
@@ -3164,25 +3290,31 @@
         <v>8</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>74</v>
+        <v>115</v>
+      </c>
+      <c r="I10" t="s">
+        <v>85</v>
+      </c>
+      <c r="J10" t="s">
+        <v>145</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>145</v>
+        <v>193</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>146</v>
+        <v>194</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>48</v>
+        <v>89</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="Q10" s="2">
         <v>1587</v>
@@ -3191,87 +3323,84 @@
         <v>1</v>
       </c>
       <c r="S10" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="U10" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="W10" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="X10" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="Y10" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="Z10" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="AA10" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="AB10" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="AC10" s="2" t="s">
-        <v>147</v>
+        <v>195</v>
       </c>
       <c r="AE10" s="2">
         <v>245</v>
       </c>
       <c r="AF10" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="AH10" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="AI10" s="2">
         <v>22</v>
       </c>
       <c r="AJ10" s="2" t="s">
-        <v>147</v>
+        <v>195</v>
       </c>
       <c r="AK10" s="2" t="s">
-        <v>148</v>
+        <v>196</v>
       </c>
       <c r="AL10" s="2" t="s">
-        <v>149</v>
+        <v>197</v>
       </c>
       <c r="AM10" s="2" t="s">
-        <v>150</v>
+        <v>198</v>
       </c>
       <c r="AN10" s="2" t="s">
-        <v>150</v>
+        <v>198</v>
       </c>
       <c r="AO10" s="2" t="s">
-        <v>151</v>
+        <v>199</v>
       </c>
       <c r="AP10" s="2" t="s">
-        <v>152</v>
+        <v>200</v>
       </c>
       <c r="AQ10" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="AR10" s="2" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="11" spans="1:44" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="11" spans="1:43" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>154</v>
+        <v>201</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>155</v>
+        <v>202</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>44</v>
+        <v>83</v>
       </c>
       <c r="F11" s="2">
         <v>9</v>
@@ -3280,25 +3409,31 @@
         <v>9</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>123</v>
+        <v>168</v>
+      </c>
+      <c r="I11" t="s">
+        <v>116</v>
+      </c>
+      <c r="J11" t="s">
+        <v>157</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>156</v>
+        <v>203</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>157</v>
+        <v>204</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>48</v>
+        <v>89</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="Q11" s="2">
         <v>1556</v>
@@ -3307,81 +3442,78 @@
         <v>1</v>
       </c>
       <c r="S11" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="U11" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="W11" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="X11" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="Y11" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="Z11" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="AA11" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="AB11" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="AF11" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="AH11" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="AI11" s="2">
         <v>18</v>
       </c>
       <c r="AJ11" s="2" t="s">
-        <v>158</v>
+        <v>205</v>
       </c>
       <c r="AK11" s="2" t="s">
-        <v>159</v>
+        <v>206</v>
       </c>
       <c r="AL11" s="2" t="s">
-        <v>160</v>
+        <v>207</v>
       </c>
       <c r="AM11" s="2" t="s">
-        <v>161</v>
+        <v>208</v>
       </c>
       <c r="AN11" s="2" t="s">
-        <v>162</v>
+        <v>209</v>
       </c>
       <c r="AO11" s="2" t="s">
-        <v>163</v>
+        <v>210</v>
       </c>
       <c r="AP11" s="2" t="s">
-        <v>164</v>
+        <v>211</v>
       </c>
       <c r="AQ11" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="AR11" s="2" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="12" spans="1:44" x14ac:dyDescent="0.25">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="12" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>165</v>
+        <v>212</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>166</v>
+        <v>213</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>44</v>
+        <v>83</v>
       </c>
       <c r="F12" s="2">
         <v>1</v>
@@ -3390,25 +3522,31 @@
         <v>1</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>111</v>
+        <v>156</v>
+      </c>
+      <c r="I12" t="s">
+        <v>214</v>
+      </c>
+      <c r="J12" t="s">
+        <v>215</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>167</v>
+        <v>216</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>168</v>
+        <v>217</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>48</v>
+        <v>89</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="Q12" s="2">
         <v>361</v>
@@ -3417,87 +3555,84 @@
         <v>3</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="U12" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="W12" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="X12" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="Y12" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="Z12" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="AA12" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="AB12" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="AE12" s="2">
         <v>61</v>
       </c>
       <c r="AF12" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="AG12" s="2">
         <v>28</v>
       </c>
       <c r="AH12" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="AI12" s="2">
         <v>6</v>
       </c>
       <c r="AJ12" s="2" t="s">
-        <v>169</v>
+        <v>218</v>
       </c>
       <c r="AK12" s="2" t="s">
-        <v>170</v>
+        <v>219</v>
       </c>
       <c r="AL12" s="2" t="s">
-        <v>171</v>
+        <v>220</v>
       </c>
       <c r="AM12" s="2" t="s">
-        <v>172</v>
+        <v>221</v>
       </c>
       <c r="AN12" s="2" t="s">
-        <v>150</v>
+        <v>198</v>
       </c>
       <c r="AO12" s="2" t="s">
-        <v>173</v>
+        <v>222</v>
       </c>
       <c r="AP12" s="2" t="s">
-        <v>174</v>
+        <v>223</v>
       </c>
       <c r="AQ12" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="AR12" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="13" spans="1:44" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>176</v>
+        <v>224</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>177</v>
+        <v>225</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>178</v>
+        <v>226</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>44</v>
+        <v>83</v>
       </c>
       <c r="F13" s="2">
         <v>5</v>
@@ -3506,25 +3641,31 @@
         <v>5</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>74</v>
+        <v>115</v>
+      </c>
+      <c r="I13" t="s">
+        <v>227</v>
+      </c>
+      <c r="J13" t="s">
+        <v>228</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>179</v>
+        <v>229</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>168</v>
+        <v>217</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>48</v>
+        <v>89</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="Q13" s="2">
         <v>396</v>
@@ -3533,93 +3674,90 @@
         <v>7</v>
       </c>
       <c r="S13" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="T13" s="2">
         <v>158</v>
       </c>
       <c r="U13" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="V13" s="2">
         <v>56</v>
       </c>
       <c r="W13" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="X13" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="Y13" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="Z13" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="AA13" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="AB13" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="AE13" s="2">
         <v>216</v>
       </c>
       <c r="AF13" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="AG13" s="2">
         <v>72</v>
       </c>
       <c r="AH13" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="AI13" s="2">
         <v>16</v>
       </c>
       <c r="AJ13" s="2" t="s">
-        <v>180</v>
+        <v>230</v>
       </c>
       <c r="AK13" s="2" t="s">
-        <v>181</v>
+        <v>231</v>
       </c>
       <c r="AL13" s="2" t="s">
-        <v>182</v>
+        <v>232</v>
       </c>
       <c r="AM13" s="2" t="s">
-        <v>183</v>
+        <v>233</v>
       </c>
       <c r="AN13" s="2" t="s">
-        <v>183</v>
+        <v>233</v>
       </c>
       <c r="AO13" s="2" t="s">
-        <v>184</v>
+        <v>234</v>
       </c>
       <c r="AP13" s="2" t="s">
-        <v>185</v>
+        <v>235</v>
       </c>
       <c r="AQ13" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="AR13" s="2" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="14" spans="1:44" x14ac:dyDescent="0.25">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="14" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>186</v>
+        <v>236</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>186</v>
+        <v>236</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>44</v>
+        <v>83</v>
       </c>
       <c r="F14" s="2">
         <v>9</v>
@@ -3628,25 +3766,31 @@
         <v>9</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>111</v>
+        <v>156</v>
+      </c>
+      <c r="I14" t="s">
+        <v>131</v>
+      </c>
+      <c r="J14" t="s">
+        <v>132</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>187</v>
+        <v>237</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>188</v>
+        <v>238</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>48</v>
+        <v>89</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="Q14" s="2">
         <v>5300</v>
@@ -3655,84 +3799,81 @@
         <v>4</v>
       </c>
       <c r="S14" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="U14" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="X14" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="Y14" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="Z14" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="AA14" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="AB14" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="AE14" s="2">
         <v>165</v>
       </c>
       <c r="AF14" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="AG14" s="2">
         <v>63</v>
       </c>
       <c r="AH14" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="AI14" s="2">
         <v>0</v>
       </c>
       <c r="AJ14" s="2" t="s">
-        <v>189</v>
+        <v>239</v>
       </c>
       <c r="AK14" s="2" t="s">
-        <v>190</v>
+        <v>240</v>
       </c>
       <c r="AL14" s="2" t="s">
-        <v>191</v>
+        <v>241</v>
       </c>
       <c r="AM14" s="2" t="s">
-        <v>192</v>
+        <v>242</v>
       </c>
       <c r="AN14" s="2" t="s">
-        <v>192</v>
+        <v>242</v>
       </c>
       <c r="AO14" s="2" t="s">
-        <v>193</v>
+        <v>243</v>
       </c>
       <c r="AP14" s="2" t="s">
-        <v>194</v>
+        <v>244</v>
       </c>
       <c r="AQ14" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="AR14" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="15" spans="1:44" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>196</v>
+        <v>245</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>196</v>
+        <v>245</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>197</v>
+        <v>246</v>
       </c>
       <c r="F15" s="2">
         <v>1</v>
@@ -3741,25 +3882,31 @@
         <v>1</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>198</v>
+        <v>247</v>
+      </c>
+      <c r="I15" t="s">
+        <v>131</v>
+      </c>
+      <c r="J15" t="s">
+        <v>132</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>199</v>
+        <v>248</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>200</v>
+        <v>249</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>48</v>
+        <v>89</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="Q15" s="2">
         <v>5013</v>
@@ -3768,84 +3915,81 @@
         <v>1</v>
       </c>
       <c r="S15" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="U15" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="X15" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="Y15" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="Z15" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="AA15" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="AB15" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="AE15" s="2">
         <v>66</v>
       </c>
       <c r="AF15" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="AG15" s="2">
         <v>50</v>
       </c>
       <c r="AH15" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="AI15" s="2">
         <v>0</v>
       </c>
       <c r="AJ15" s="2" t="s">
-        <v>201</v>
+        <v>250</v>
       </c>
       <c r="AK15" s="2" t="s">
-        <v>202</v>
+        <v>251</v>
       </c>
       <c r="AL15" s="2" t="s">
-        <v>203</v>
+        <v>252</v>
       </c>
       <c r="AM15" s="2" t="s">
-        <v>192</v>
+        <v>242</v>
       </c>
       <c r="AN15" s="2" t="s">
-        <v>204</v>
+        <v>253</v>
       </c>
       <c r="AO15" s="2" t="s">
-        <v>193</v>
+        <v>243</v>
       </c>
       <c r="AP15" s="2" t="s">
-        <v>194</v>
+        <v>244</v>
       </c>
       <c r="AQ15" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="AR15" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="16" spans="1:44" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>205</v>
+        <v>254</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>206</v>
+        <v>255</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>207</v>
+        <v>256</v>
       </c>
       <c r="F16" s="2">
         <v>1</v>
@@ -3854,25 +3998,31 @@
         <v>3</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>123</v>
+        <v>168</v>
+      </c>
+      <c r="I16" t="s">
+        <v>144</v>
+      </c>
+      <c r="J16" t="s">
+        <v>257</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>208</v>
+        <v>258</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>209</v>
+        <v>259</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>48</v>
+        <v>89</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="Q16" s="2">
         <v>60</v>
@@ -3881,84 +4031,81 @@
         <v>1</v>
       </c>
       <c r="S16" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="T16" s="2">
         <v>10</v>
       </c>
       <c r="U16" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="W16" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="X16" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="Y16" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="Z16" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="AA16" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="AB16" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="AF16" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="AH16" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="AI16" s="2">
         <v>4</v>
       </c>
       <c r="AJ16" s="2" t="s">
-        <v>210</v>
+        <v>260</v>
       </c>
       <c r="AK16" s="2" t="s">
-        <v>211</v>
+        <v>261</v>
       </c>
       <c r="AL16" s="2" t="s">
-        <v>212</v>
+        <v>262</v>
       </c>
       <c r="AM16" s="2" t="s">
-        <v>213</v>
+        <v>263</v>
       </c>
       <c r="AN16" s="2" t="s">
-        <v>213</v>
+        <v>263</v>
       </c>
       <c r="AO16" s="2" t="s">
-        <v>214</v>
+        <v>264</v>
       </c>
       <c r="AP16" s="2" t="s">
-        <v>215</v>
+        <v>265</v>
       </c>
       <c r="AQ16" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="AR16" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="17" spans="1:44" x14ac:dyDescent="0.25">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="17" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>216</v>
+        <v>266</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>217</v>
+        <v>267</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>44</v>
+        <v>83</v>
       </c>
       <c r="F17" s="2">
         <v>1</v>
@@ -3967,25 +4114,31 @@
         <v>1</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>74</v>
+        <v>115</v>
+      </c>
+      <c r="I17" t="s">
+        <v>227</v>
+      </c>
+      <c r="J17" t="s">
+        <v>268</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>167</v>
+        <v>216</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>219</v>
+        <v>269</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>48</v>
+        <v>89</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="Q17" s="2">
         <v>3518</v>
@@ -3994,84 +4147,81 @@
         <v>2</v>
       </c>
       <c r="S17" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="U17" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="W17" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="X17" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="Y17" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="Z17" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="AA17" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="AB17" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="AE17" s="2">
         <v>125</v>
       </c>
       <c r="AF17" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="AH17" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="AI17" s="2">
         <v>10</v>
       </c>
       <c r="AJ17" s="2" t="s">
-        <v>220</v>
+        <v>270</v>
       </c>
       <c r="AK17" s="2" t="s">
-        <v>221</v>
+        <v>271</v>
       </c>
       <c r="AL17" s="2" t="s">
-        <v>222</v>
+        <v>272</v>
       </c>
       <c r="AM17" s="2" t="s">
-        <v>223</v>
+        <v>273</v>
       </c>
       <c r="AN17" s="2" t="s">
-        <v>224</v>
+        <v>274</v>
       </c>
       <c r="AO17" s="2" t="s">
-        <v>225</v>
+        <v>275</v>
       </c>
       <c r="AP17" s="2" t="s">
-        <v>226</v>
+        <v>276</v>
       </c>
       <c r="AQ17" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="AR17" s="2" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="18" spans="1:44" x14ac:dyDescent="0.25">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="18" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>228</v>
+        <v>277</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>228</v>
+        <v>277</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>229</v>
+        <v>278</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>44</v>
+        <v>83</v>
       </c>
       <c r="F18" s="2">
         <v>1</v>
@@ -4080,96 +4230,99 @@
         <v>1</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>230</v>
+        <v>279</v>
+      </c>
+      <c r="I18" t="s">
+        <v>153</v>
+      </c>
+      <c r="J18" t="s">
+        <v>280</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>231</v>
+        <v>281</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>232</v>
+        <v>282</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>48</v>
+        <v>89</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="X18" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="Y18" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="Z18" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="AA18" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="AB18" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="AE18" s="2">
         <v>74</v>
       </c>
       <c r="AF18" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="AG18" s="2">
         <v>50</v>
       </c>
       <c r="AH18" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="AI18" s="2">
         <v>0</v>
       </c>
       <c r="AJ18" s="2" t="s">
-        <v>233</v>
+        <v>283</v>
       </c>
       <c r="AK18" s="2" t="s">
-        <v>234</v>
+        <v>284</v>
       </c>
       <c r="AL18" s="2" t="s">
-        <v>235</v>
+        <v>285</v>
       </c>
       <c r="AM18" s="2" t="s">
-        <v>236</v>
+        <v>286</v>
       </c>
       <c r="AN18" s="2" t="s">
-        <v>236</v>
+        <v>286</v>
       </c>
       <c r="AO18" s="2" t="s">
-        <v>237</v>
+        <v>287</v>
       </c>
       <c r="AQ18" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="AR18" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="19" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="19" spans="1:43" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>239</v>
+        <v>288</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>240</v>
+        <v>289</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>241</v>
+        <v>290</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>44</v>
+        <v>83</v>
       </c>
       <c r="F19" s="2">
         <v>2</v>
@@ -4178,25 +4331,31 @@
         <v>3</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>242</v>
+        <v>291</v>
+      </c>
+      <c r="I19" t="s">
+        <v>292</v>
+      </c>
+      <c r="J19" t="s">
+        <v>169</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>243</v>
+        <v>293</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>244</v>
+        <v>294</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>48</v>
+        <v>89</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="Q19" s="2">
         <v>510</v>
@@ -4205,93 +4364,90 @@
         <v>3</v>
       </c>
       <c r="S19" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="T19" s="2">
         <v>32</v>
       </c>
       <c r="U19" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="V19" s="2">
         <v>3</v>
       </c>
       <c r="W19" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="X19" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="Y19" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="Z19" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="AA19" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="AB19" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="AE19" s="2">
         <v>147</v>
       </c>
       <c r="AF19" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="AG19" s="2">
         <v>49</v>
       </c>
       <c r="AH19" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="AI19" s="2">
         <v>10</v>
       </c>
       <c r="AJ19" s="2" t="s">
-        <v>246</v>
+        <v>295</v>
       </c>
       <c r="AK19" s="2" t="s">
-        <v>247</v>
+        <v>296</v>
       </c>
       <c r="AL19" s="2" t="s">
-        <v>248</v>
+        <v>297</v>
       </c>
       <c r="AM19" s="2" t="s">
-        <v>249</v>
+        <v>298</v>
       </c>
       <c r="AN19" s="2" t="s">
-        <v>249</v>
+        <v>298</v>
       </c>
       <c r="AO19" s="2" t="s">
-        <v>250</v>
+        <v>299</v>
       </c>
       <c r="AP19" s="2" t="s">
-        <v>251</v>
+        <v>300</v>
       </c>
       <c r="AQ19" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="AR19" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="20" spans="1:44" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>252</v>
+        <v>301</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>253</v>
+        <v>302</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>44</v>
+        <v>83</v>
       </c>
       <c r="F20" s="2">
         <v>2</v>
@@ -4300,25 +4456,31 @@
         <v>3</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>74</v>
+        <v>115</v>
+      </c>
+      <c r="I20" t="s">
+        <v>181</v>
+      </c>
+      <c r="J20" t="s">
+        <v>303</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>254</v>
+        <v>304</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>255</v>
+        <v>305</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>48</v>
+        <v>89</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="Q20" s="2">
         <v>420</v>
@@ -4327,90 +4489,87 @@
         <v>3</v>
       </c>
       <c r="S20" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="T20" s="2">
         <v>37</v>
       </c>
       <c r="U20" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="V20" s="2">
         <v>6</v>
       </c>
       <c r="W20" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="X20" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="Y20" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="Z20" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="AA20" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="AB20" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="AC20" s="2" t="s">
-        <v>489</v>
+        <v>306</v>
       </c>
       <c r="AF20" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="AH20" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="AI20" s="2">
         <v>12</v>
       </c>
       <c r="AJ20" s="2" t="s">
-        <v>256</v>
+        <v>307</v>
       </c>
       <c r="AK20" s="2" t="s">
-        <v>257</v>
+        <v>308</v>
       </c>
       <c r="AL20" s="2" t="s">
-        <v>258</v>
+        <v>309</v>
       </c>
       <c r="AM20" s="2" t="s">
-        <v>68</v>
+        <v>109</v>
       </c>
       <c r="AN20" s="2" t="s">
-        <v>68</v>
+        <v>109</v>
       </c>
       <c r="AO20" s="2" t="s">
-        <v>193</v>
+        <v>243</v>
       </c>
       <c r="AP20" s="2" t="s">
-        <v>259</v>
+        <v>310</v>
       </c>
       <c r="AQ20" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="AR20" s="2" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="21" spans="1:44" x14ac:dyDescent="0.25">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="21" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>261</v>
+        <v>311</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>262</v>
+        <v>312</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>229</v>
+        <v>278</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>263</v>
+        <v>313</v>
       </c>
       <c r="F21" s="2">
         <v>1</v>
@@ -4419,25 +4578,31 @@
         <v>1</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>230</v>
+        <v>279</v>
+      </c>
+      <c r="I21" t="s">
+        <v>153</v>
+      </c>
+      <c r="J21" t="s">
+        <v>314</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>264</v>
+        <v>315</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>265</v>
+        <v>316</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>48</v>
+        <v>89</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="Q21" s="2">
         <v>8886</v>
@@ -4446,167 +4611,167 @@
         <v>1</v>
       </c>
       <c r="S21" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="U21" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="W21" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="X21" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="Y21" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="Z21" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="AA21" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="AB21" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="AC21" s="2" t="s">
-        <v>489</v>
+        <v>306</v>
       </c>
       <c r="AF21" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="AH21" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="AI21" s="2">
         <v>0</v>
       </c>
       <c r="AJ21" s="2" t="s">
-        <v>266</v>
+        <v>317</v>
       </c>
       <c r="AK21" s="2" t="s">
-        <v>267</v>
+        <v>318</v>
       </c>
       <c r="AM21" s="2" t="s">
-        <v>268</v>
+        <v>319</v>
       </c>
       <c r="AO21" s="2" t="s">
-        <v>269</v>
+        <v>320</v>
       </c>
       <c r="AP21" s="2" t="s">
-        <v>270</v>
+        <v>321</v>
       </c>
       <c r="AQ21" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="AR21" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="22" spans="1:44" x14ac:dyDescent="0.25">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="22" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>271</v>
+        <v>322</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>272</v>
+        <v>323</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>273</v>
+        <v>324</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>274</v>
+        <v>325</v>
       </c>
       <c r="F22" s="2">
         <v>1</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>275</v>
+        <v>326</v>
+      </c>
+      <c r="I22" t="s">
+        <v>131</v>
+      </c>
+      <c r="J22" t="s">
+        <v>327</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>276</v>
+        <v>328</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>277</v>
+        <v>329</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>48</v>
+        <v>89</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="R22" s="2">
         <v>1</v>
       </c>
       <c r="S22" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="X22" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="Y22" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="Z22" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="AA22" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="AB22" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="AC22" s="2" t="s">
-        <v>489</v>
+        <v>306</v>
       </c>
       <c r="AI22" s="2">
         <v>0</v>
       </c>
       <c r="AJ22" s="2" t="s">
-        <v>278</v>
+        <v>330</v>
       </c>
       <c r="AK22" s="2" t="s">
-        <v>279</v>
+        <v>331</v>
       </c>
       <c r="AM22" s="2" t="s">
-        <v>268</v>
+        <v>319</v>
       </c>
       <c r="AO22" s="2" t="s">
-        <v>280</v>
+        <v>332</v>
       </c>
       <c r="AP22" s="2" t="s">
-        <v>270</v>
+        <v>321</v>
       </c>
       <c r="AQ22" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="AR22" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="23" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>281</v>
+        <v>333</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>282</v>
+        <v>334</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>44</v>
+        <v>83</v>
       </c>
       <c r="F23" s="2">
         <v>4</v>
@@ -4615,25 +4780,31 @@
         <v>9</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>74</v>
+        <v>115</v>
+      </c>
+      <c r="I23" t="s">
+        <v>227</v>
+      </c>
+      <c r="J23" t="s">
+        <v>335</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>283</v>
+        <v>336</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>284</v>
+        <v>337</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>48</v>
+        <v>89</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="Q23" s="2">
         <v>434</v>
@@ -4642,87 +4813,81 @@
         <v>4</v>
       </c>
       <c r="S23" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="T23" s="2">
         <v>8</v>
       </c>
       <c r="U23" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="V23" s="2">
         <v>5</v>
       </c>
       <c r="W23" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="X23" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="Y23" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="Z23" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="AA23" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="AB23" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="AF23" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="AH23" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="AI23" s="2">
         <v>10</v>
       </c>
       <c r="AJ23" s="2" t="s">
-        <v>500</v>
+        <v>338</v>
       </c>
       <c r="AK23" s="2" t="s">
-        <v>501</v>
+        <v>339</v>
       </c>
       <c r="AL23" s="2" t="s">
-        <v>502</v>
+        <v>340</v>
       </c>
       <c r="AM23" s="2" t="s">
-        <v>496</v>
-      </c>
-      <c r="AN23" s="2" t="s">
-        <v>497</v>
+        <v>341</v>
       </c>
       <c r="AO23" s="2" t="s">
-        <v>498</v>
+        <v>342</v>
       </c>
       <c r="AP23" s="2" t="s">
-        <v>499</v>
+        <v>343</v>
       </c>
       <c r="AQ23" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="AR23" s="2" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="24" spans="1:44" x14ac:dyDescent="0.25">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="24" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>285</v>
+        <v>344</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>286</v>
+        <v>345</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>287</v>
+        <v>127</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>44</v>
+        <v>83</v>
       </c>
       <c r="F24" s="2">
         <v>2</v>
@@ -4731,25 +4896,31 @@
         <v>9</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>288</v>
+        <v>346</v>
+      </c>
+      <c r="I24" t="s">
+        <v>181</v>
+      </c>
+      <c r="J24" t="s">
+        <v>347</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>482</v>
+        <v>348</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>290</v>
+        <v>349</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>48</v>
+        <v>89</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="Q24" s="2">
         <v>2006</v>
@@ -4758,78 +4929,75 @@
         <v>1</v>
       </c>
       <c r="S24" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="U24" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="W24" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="X24" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="Y24" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="Z24" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="AA24" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="AB24" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="AF24" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="AH24" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="AJ24" s="2" t="s">
-        <v>291</v>
+        <v>350</v>
       </c>
       <c r="AK24" s="2" t="s">
-        <v>292</v>
+        <v>351</v>
       </c>
       <c r="AL24" s="2" t="s">
-        <v>293</v>
+        <v>352</v>
       </c>
       <c r="AM24" s="2" t="s">
-        <v>294</v>
+        <v>353</v>
       </c>
       <c r="AN24" s="2" t="s">
-        <v>495</v>
+        <v>354</v>
       </c>
       <c r="AO24" s="2" t="s">
-        <v>193</v>
+        <v>243</v>
       </c>
       <c r="AP24" s="2" t="s">
-        <v>259</v>
+        <v>310</v>
       </c>
       <c r="AQ24" s="2" t="s">
-        <v>504</v>
-      </c>
-      <c r="AR24" s="2" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="25" spans="1:44" x14ac:dyDescent="0.25">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="25" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>295</v>
+        <v>355</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>296</v>
+        <v>356</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>287</v>
+        <v>127</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>44</v>
+        <v>83</v>
       </c>
       <c r="F25" s="2">
         <v>2</v>
@@ -4838,25 +5006,31 @@
         <v>4</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>479</v>
+        <v>357</v>
+      </c>
+      <c r="I25" t="s">
+        <v>227</v>
+      </c>
+      <c r="J25" t="s">
+        <v>145</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>487</v>
+        <v>358</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>297</v>
+        <v>359</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>48</v>
+        <v>89</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="Q25" s="2">
         <v>1463</v>
@@ -4865,78 +5039,75 @@
         <v>1</v>
       </c>
       <c r="S25" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="U25" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="W25" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="X25" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="Y25" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="Z25" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="AA25" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="AB25" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="AF25" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="AH25" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="AJ25" s="2" t="s">
-        <v>298</v>
+        <v>360</v>
       </c>
       <c r="AK25" s="2" t="s">
-        <v>299</v>
+        <v>361</v>
       </c>
       <c r="AL25" s="2" t="s">
-        <v>300</v>
+        <v>362</v>
       </c>
       <c r="AM25" s="2" t="s">
-        <v>301</v>
+        <v>363</v>
       </c>
       <c r="AN25" s="2" t="s">
-        <v>301</v>
+        <v>363</v>
       </c>
       <c r="AO25" s="2" t="s">
-        <v>506</v>
+        <v>364</v>
       </c>
       <c r="AP25" s="4" t="s">
-        <v>505</v>
+        <v>365</v>
       </c>
       <c r="AQ25" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="AR25" s="2" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="26" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="26" spans="1:43" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>302</v>
+        <v>366</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>303</v>
+        <v>367</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>44</v>
+        <v>83</v>
       </c>
       <c r="F26" s="2">
         <v>2</v>
@@ -4945,25 +5116,31 @@
         <v>4</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>304</v>
+        <v>368</v>
+      </c>
+      <c r="I26" t="s">
+        <v>116</v>
+      </c>
+      <c r="J26" t="s">
+        <v>369</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>485</v>
+        <v>370</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>484</v>
+        <v>371</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>48</v>
+        <v>89</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="Q26" s="2">
         <v>472</v>
@@ -4972,93 +5149,90 @@
         <v>2</v>
       </c>
       <c r="S26" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="T26" s="2">
         <v>24</v>
       </c>
       <c r="U26" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="V26" s="2">
         <v>4</v>
       </c>
       <c r="W26" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="X26" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="Y26" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="Z26" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="AA26" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="AB26" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="AC26" s="2" t="s">
-        <v>490</v>
+        <v>372</v>
       </c>
       <c r="AE26" s="2">
         <v>186</v>
       </c>
       <c r="AF26" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="AG26" s="2">
         <v>35</v>
       </c>
       <c r="AH26" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="AI26" s="2">
         <v>12</v>
       </c>
       <c r="AJ26" s="2" t="s">
-        <v>305</v>
+        <v>373</v>
       </c>
       <c r="AK26" s="2" t="s">
-        <v>306</v>
+        <v>374</v>
       </c>
       <c r="AL26" s="2" t="s">
-        <v>307</v>
+        <v>375</v>
       </c>
       <c r="AM26" s="2" t="s">
-        <v>308</v>
+        <v>376</v>
       </c>
       <c r="AO26" s="2" t="s">
-        <v>491</v>
+        <v>377</v>
       </c>
       <c r="AP26" s="4" t="s">
-        <v>492</v>
+        <v>378</v>
       </c>
       <c r="AQ26" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="AR26" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="27" spans="1:44" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>309</v>
+        <v>379</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>310</v>
+        <v>380</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>43</v>
+        <v>82</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>44</v>
+        <v>83</v>
       </c>
       <c r="F27" s="2">
         <v>1</v>
@@ -5067,25 +5241,31 @@
         <v>33</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>480</v>
+        <v>381</v>
+      </c>
+      <c r="I27" t="s">
+        <v>116</v>
+      </c>
+      <c r="J27" t="s">
+        <v>169</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>481</v>
+        <v>382</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>483</v>
+        <v>383</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>48</v>
+        <v>89</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="Q27" s="2">
         <v>1674</v>
@@ -5094,78 +5274,75 @@
         <v>1</v>
       </c>
       <c r="S27" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="U27" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="W27" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="X27" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="Y27" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="Z27" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="AA27" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="AB27" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="AF27" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="AH27" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="AJ27" s="2" t="s">
-        <v>311</v>
+        <v>384</v>
       </c>
       <c r="AK27" s="2" t="s">
-        <v>312</v>
+        <v>385</v>
       </c>
       <c r="AL27" s="2" t="s">
-        <v>313</v>
+        <v>386</v>
       </c>
       <c r="AM27" s="2" t="s">
-        <v>314</v>
+        <v>387</v>
       </c>
       <c r="AN27" s="2" t="s">
-        <v>494</v>
+        <v>388</v>
       </c>
       <c r="AO27" s="2" t="s">
-        <v>507</v>
+        <v>389</v>
       </c>
       <c r="AP27" s="4" t="s">
-        <v>508</v>
+        <v>390</v>
       </c>
       <c r="AQ27" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="AR27" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="28" spans="1:44" x14ac:dyDescent="0.25">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="28" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>315</v>
+        <v>391</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>316</v>
+        <v>392</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>44</v>
+        <v>83</v>
       </c>
       <c r="F28" s="2">
         <v>14</v>
@@ -5174,25 +5351,31 @@
         <v>40</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>317</v>
+        <v>393</v>
+      </c>
+      <c r="I28" t="s">
+        <v>116</v>
+      </c>
+      <c r="J28" t="s">
+        <v>157</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>486</v>
+        <v>394</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>318</v>
+        <v>395</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>245</v>
+        <v>396</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="P28" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="Q28" s="2">
         <v>3382</v>
@@ -5201,77 +5384,74 @@
         <v>1</v>
       </c>
       <c r="S28" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="T28" s="2">
         <v>80</v>
       </c>
       <c r="U28" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="V28" s="2">
         <v>28</v>
       </c>
       <c r="W28" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="X28" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="Y28" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="Z28" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="AA28" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="AB28" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="AC28" s="2" t="s">
-        <v>489</v>
+        <v>306</v>
       </c>
       <c r="AF28" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="AH28" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="AJ28" s="2" t="s">
-        <v>319</v>
+        <v>397</v>
       </c>
       <c r="AK28" s="2" t="s">
-        <v>320</v>
+        <v>398</v>
       </c>
       <c r="AL28" s="2" t="s">
-        <v>493</v>
+        <v>399</v>
       </c>
       <c r="AM28" s="2" t="s">
-        <v>321</v>
+        <v>400</v>
       </c>
       <c r="AN28" s="2" t="s">
-        <v>162</v>
+        <v>209</v>
       </c>
       <c r="AO28" s="2" t="s">
-        <v>509</v>
+        <v>401</v>
       </c>
       <c r="AP28" s="2" t="s">
-        <v>510</v>
+        <v>402</v>
       </c>
       <c r="AQ28" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="AR28" s="2" t="s">
-        <v>141</v>
+        <v>189</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="AP26" r:id="rId1" xr:uid="{443AC83C-9B84-4E55-8A59-C289759413E4}"/>
-    <hyperlink ref="AP25" r:id="rId2" xr:uid="{C5CCC31E-1889-43BD-81B9-B1C9AF7728E4}"/>
-    <hyperlink ref="AP27" r:id="rId3" xr:uid="{6DFAAF02-8AD1-464D-882A-109137A57C9C}"/>
+    <hyperlink ref="AP25" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="AP26" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="AP27" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5292,22 +5472,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>476</v>
+        <v>539</v>
       </c>
       <c r="B1" t="s">
-        <v>477</v>
+        <v>540</v>
       </c>
       <c r="C1" t="s">
-        <v>529</v>
+        <v>541</v>
       </c>
       <c r="D1" t="s">
-        <v>478</v>
+        <v>542</v>
       </c>
       <c r="E1" t="s">
-        <v>548</v>
+        <v>543</v>
       </c>
       <c r="F1" t="s">
-        <v>33</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -5315,19 +5495,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>519</v>
+        <v>544</v>
       </c>
       <c r="C2" t="s">
-        <v>530</v>
+        <v>545</v>
       </c>
       <c r="D2" t="s">
-        <v>520</v>
+        <v>546</v>
       </c>
       <c r="E2" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="F2" t="s">
-        <v>538</v>
+        <v>548</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -5335,19 +5515,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="C3" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="D3" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="E3" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="F3" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -5355,19 +5535,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>524</v>
+        <v>553</v>
       </c>
       <c r="C4" t="s">
-        <v>524</v>
+        <v>553</v>
       </c>
       <c r="D4" t="s">
-        <v>525</v>
+        <v>554</v>
       </c>
       <c r="E4" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="F4" t="s">
-        <v>539</v>
+        <v>555</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -5375,19 +5555,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>532</v>
+        <v>556</v>
       </c>
       <c r="C5" t="s">
-        <v>526</v>
+        <v>557</v>
       </c>
       <c r="D5" t="s">
-        <v>525</v>
+        <v>554</v>
       </c>
       <c r="E5" t="s">
-        <v>550</v>
+        <v>558</v>
       </c>
       <c r="F5" t="s">
-        <v>540</v>
+        <v>559</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -5395,19 +5575,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>527</v>
+        <v>560</v>
       </c>
       <c r="C6" t="s">
-        <v>531</v>
+        <v>561</v>
       </c>
       <c r="D6" t="s">
-        <v>536</v>
+        <v>562</v>
       </c>
       <c r="E6" t="s">
-        <v>550</v>
+        <v>558</v>
       </c>
       <c r="F6" t="s">
-        <v>541</v>
+        <v>563</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -5415,19 +5595,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>528</v>
+        <v>564</v>
       </c>
       <c r="C7" t="s">
-        <v>533</v>
+        <v>565</v>
       </c>
       <c r="D7" t="s">
-        <v>536</v>
+        <v>562</v>
       </c>
       <c r="E7" t="s">
-        <v>550</v>
+        <v>558</v>
       </c>
       <c r="F7" t="s">
-        <v>542</v>
+        <v>566</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -5435,19 +5615,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>535</v>
+        <v>567</v>
       </c>
       <c r="C8" t="s">
-        <v>534</v>
+        <v>568</v>
       </c>
       <c r="D8" t="s">
-        <v>536</v>
+        <v>562</v>
       </c>
       <c r="E8" t="s">
-        <v>550</v>
+        <v>558</v>
       </c>
       <c r="F8" t="s">
-        <v>543</v>
+        <v>569</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -5455,16 +5635,1009 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>537</v>
+        <v>570</v>
       </c>
       <c r="D9" t="s">
-        <v>552</v>
+        <v>571</v>
       </c>
       <c r="E9" t="s">
-        <v>551</v>
+        <v>572</v>
       </c>
       <c r="F9" t="s">
-        <v>544</v>
+        <v>573</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="66.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="107.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>574</v>
+      </c>
+      <c r="B1" t="s">
+        <v>575</v>
+      </c>
+      <c r="C1" t="s">
+        <v>576</v>
+      </c>
+      <c r="D1" t="s">
+        <v>469</v>
+      </c>
+      <c r="E1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>577</v>
+      </c>
+      <c r="C2" t="s">
+        <v>578</v>
+      </c>
+      <c r="D2" t="s">
+        <v>579</v>
+      </c>
+      <c r="E2" t="s">
+        <v>580</v>
+      </c>
+      <c r="F2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>582</v>
+      </c>
+      <c r="C3" t="s">
+        <v>583</v>
+      </c>
+      <c r="D3" t="s">
+        <v>584</v>
+      </c>
+      <c r="E3" s="5">
+        <v>45931</v>
+      </c>
+      <c r="F3" t="s">
+        <v>585</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="24.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>586</v>
+      </c>
+      <c r="B1" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>292</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
+  <dimension ref="A1:B28"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>7</v>
+      </c>
+      <c r="B7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>9</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>10</v>
+      </c>
+      <c r="B10">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>11</v>
+      </c>
+      <c r="B11">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>12</v>
+      </c>
+      <c r="B12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>13</v>
+      </c>
+      <c r="B13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>14</v>
+      </c>
+      <c r="B14">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>15</v>
+      </c>
+      <c r="B15">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>16</v>
+      </c>
+      <c r="B16">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>17</v>
+      </c>
+      <c r="B17">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>18</v>
+      </c>
+      <c r="B18">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>19</v>
+      </c>
+      <c r="B19">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>20</v>
+      </c>
+      <c r="B20">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>21</v>
+      </c>
+      <c r="B21">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>22</v>
+      </c>
+      <c r="B22">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>23</v>
+      </c>
+      <c r="B23">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>24</v>
+      </c>
+      <c r="B24">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>25</v>
+      </c>
+      <c r="B25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>26</v>
+      </c>
+      <c r="B26">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
+  <dimension ref="A1:B28"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
+  <dimension ref="A1:B43"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>586</v>
+      </c>
+      <c r="B1" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>2</v>
+      </c>
+      <c r="B8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>2</v>
+      </c>
+      <c r="B9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>2</v>
+      </c>
+      <c r="B10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>2</v>
+      </c>
+      <c r="B11">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>2</v>
+      </c>
+      <c r="B12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>2</v>
+      </c>
+      <c r="B13">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>2</v>
+      </c>
+      <c r="B14">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>3</v>
+      </c>
+      <c r="B15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>3</v>
+      </c>
+      <c r="B16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>3</v>
+      </c>
+      <c r="B17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>4</v>
+      </c>
+      <c r="B18">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>4</v>
+      </c>
+      <c r="B19">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>4</v>
+      </c>
+      <c r="B20">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>5</v>
+      </c>
+      <c r="B21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>5</v>
+      </c>
+      <c r="B22">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>5</v>
+      </c>
+      <c r="B23">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>5</v>
+      </c>
+      <c r="B24">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>5</v>
+      </c>
+      <c r="B25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>5</v>
+      </c>
+      <c r="B26">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>6</v>
+      </c>
+      <c r="B27">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>6</v>
+      </c>
+      <c r="B28">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>6</v>
+      </c>
+      <c r="B29">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>6</v>
+      </c>
+      <c r="B30">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>7</v>
+      </c>
+      <c r="B31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>7</v>
+      </c>
+      <c r="B32">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>7</v>
+      </c>
+      <c r="B33">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>7</v>
+      </c>
+      <c r="B34">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>7</v>
+      </c>
+      <c r="B35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>7</v>
+      </c>
+      <c r="B36">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>8</v>
+      </c>
+      <c r="B37">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>8</v>
+      </c>
+      <c r="B38">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>8</v>
+      </c>
+      <c r="B39">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>9</v>
+      </c>
+      <c r="B40">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>9</v>
+      </c>
+      <c r="B41">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>9</v>
+      </c>
+      <c r="B42">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>9</v>
+      </c>
+      <c r="B43">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -5486,22 +6659,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>322</v>
+        <v>403</v>
       </c>
       <c r="B1" t="s">
-        <v>323</v>
+        <v>404</v>
       </c>
       <c r="C1" t="s">
-        <v>324</v>
+        <v>405</v>
       </c>
       <c r="D1" t="s">
-        <v>325</v>
+        <v>406</v>
       </c>
       <c r="E1" t="s">
-        <v>326</v>
+        <v>407</v>
       </c>
       <c r="F1" t="s">
-        <v>327</v>
+        <v>408</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -5509,19 +6682,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>328</v>
+        <v>409</v>
       </c>
       <c r="C2" t="s">
-        <v>329</v>
+        <v>410</v>
       </c>
       <c r="D2" t="s">
-        <v>330</v>
+        <v>411</v>
       </c>
       <c r="E2" t="s">
-        <v>329</v>
+        <v>410</v>
       </c>
       <c r="F2" t="s">
-        <v>329</v>
+        <v>410</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -5529,19 +6702,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>331</v>
+        <v>412</v>
       </c>
       <c r="C3" t="s">
-        <v>330</v>
+        <v>411</v>
       </c>
       <c r="D3" t="s">
-        <v>330</v>
+        <v>411</v>
       </c>
       <c r="E3" t="s">
-        <v>330</v>
+        <v>411</v>
       </c>
       <c r="F3" t="s">
-        <v>330</v>
+        <v>411</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -5549,19 +6722,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>332</v>
+        <v>413</v>
       </c>
       <c r="C4" t="s">
-        <v>333</v>
+        <v>414</v>
       </c>
       <c r="D4" t="s">
-        <v>333</v>
+        <v>414</v>
       </c>
       <c r="E4" t="s">
-        <v>333</v>
+        <v>414</v>
       </c>
       <c r="F4" t="s">
-        <v>333</v>
+        <v>414</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -5569,19 +6742,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>334</v>
+        <v>415</v>
       </c>
       <c r="C5" t="s">
-        <v>330</v>
+        <v>411</v>
       </c>
       <c r="D5" t="s">
-        <v>335</v>
+        <v>416</v>
       </c>
       <c r="E5" t="s">
-        <v>330</v>
+        <v>411</v>
       </c>
       <c r="F5" t="s">
-        <v>330</v>
+        <v>411</v>
       </c>
     </row>
   </sheetData>
@@ -5591,7 +6764,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="15.85546875" bestFit="1" customWidth="1"/>
@@ -5601,16 +6774,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>336</v>
+        <v>417</v>
       </c>
       <c r="B1" t="s">
-        <v>337</v>
+        <v>418</v>
       </c>
       <c r="C1" t="s">
-        <v>338</v>
+        <v>419</v>
       </c>
       <c r="D1" t="s">
-        <v>339</v>
+        <v>420</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -5618,13 +6791,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>340</v>
+        <v>421</v>
       </c>
       <c r="C2" t="s">
-        <v>341</v>
+        <v>422</v>
       </c>
       <c r="D2" t="s">
-        <v>342</v>
+        <v>423</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -5632,13 +6805,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>289</v>
+        <v>424</v>
       </c>
       <c r="C3" t="s">
-        <v>341</v>
+        <v>422</v>
       </c>
       <c r="D3" t="s">
-        <v>342</v>
+        <v>423</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -5646,13 +6819,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>264</v>
+        <v>315</v>
       </c>
       <c r="C4" t="s">
-        <v>343</v>
+        <v>425</v>
       </c>
       <c r="D4" t="s">
-        <v>342</v>
+        <v>423</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -5660,13 +6833,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>344</v>
+        <v>426</v>
       </c>
       <c r="C5" t="s">
-        <v>343</v>
+        <v>425</v>
       </c>
       <c r="D5" t="s">
-        <v>335</v>
+        <v>416</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -5674,13 +6847,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>345</v>
+        <v>427</v>
       </c>
       <c r="C6" t="s">
-        <v>346</v>
+        <v>428</v>
       </c>
       <c r="D6" t="s">
-        <v>335</v>
+        <v>416</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -5688,13 +6861,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>347</v>
+        <v>429</v>
       </c>
       <c r="C7" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="D7" t="s">
-        <v>342</v>
+        <v>423</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -5702,13 +6875,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>349</v>
+        <v>431</v>
       </c>
       <c r="C8" t="s">
-        <v>350</v>
+        <v>432</v>
       </c>
       <c r="D8" t="s">
-        <v>342</v>
+        <v>423</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -5716,13 +6889,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>351</v>
+        <v>433</v>
       </c>
       <c r="C9" t="s">
-        <v>350</v>
+        <v>432</v>
       </c>
       <c r="D9" t="s">
-        <v>342</v>
+        <v>423</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -5730,13 +6903,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>352</v>
+        <v>434</v>
       </c>
       <c r="C10" t="s">
-        <v>353</v>
+        <v>435</v>
       </c>
       <c r="D10" t="s">
-        <v>342</v>
+        <v>423</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -5744,13 +6917,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>354</v>
+        <v>436</v>
       </c>
       <c r="C11" t="s">
-        <v>353</v>
+        <v>435</v>
       </c>
       <c r="D11" t="s">
-        <v>342</v>
+        <v>423</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -5758,13 +6931,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>355</v>
+        <v>437</v>
       </c>
       <c r="C12" t="s">
-        <v>353</v>
+        <v>435</v>
       </c>
       <c r="D12" t="s">
-        <v>342</v>
+        <v>423</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -5772,13 +6945,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>356</v>
+        <v>438</v>
       </c>
       <c r="C13" t="s">
-        <v>357</v>
+        <v>439</v>
       </c>
       <c r="D13" t="s">
-        <v>342</v>
+        <v>423</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -5786,13 +6959,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>231</v>
+        <v>281</v>
       </c>
       <c r="C14" t="s">
-        <v>358</v>
+        <v>440</v>
       </c>
       <c r="D14" t="s">
-        <v>342</v>
+        <v>423</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -5800,13 +6973,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>359</v>
+        <v>441</v>
       </c>
       <c r="C15" t="s">
-        <v>360</v>
+        <v>442</v>
       </c>
       <c r="D15" t="s">
-        <v>342</v>
+        <v>423</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -5814,13 +6987,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>361</v>
+        <v>443</v>
       </c>
       <c r="C16" t="s">
-        <v>360</v>
+        <v>442</v>
       </c>
       <c r="D16" t="s">
-        <v>342</v>
+        <v>423</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -5828,13 +7001,111 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>362</v>
+        <v>444</v>
       </c>
       <c r="C17" t="s">
-        <v>353</v>
+        <v>435</v>
       </c>
       <c r="D17" t="s">
-        <v>342</v>
+        <v>423</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>445</v>
+      </c>
+      <c r="C18" t="s">
+        <v>435</v>
+      </c>
+      <c r="D18" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>446</v>
+      </c>
+      <c r="C19" t="s">
+        <v>435</v>
+      </c>
+      <c r="D19" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>447</v>
+      </c>
+      <c r="C20" t="s">
+        <v>435</v>
+      </c>
+      <c r="D20" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>448</v>
+      </c>
+      <c r="C21" t="s">
+        <v>449</v>
+      </c>
+      <c r="D21" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>450</v>
+      </c>
+      <c r="C22" t="s">
+        <v>449</v>
+      </c>
+      <c r="D22" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>451</v>
+      </c>
+      <c r="C23" t="s">
+        <v>449</v>
+      </c>
+      <c r="D23" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>452</v>
+      </c>
+      <c r="C24" t="s">
+        <v>453</v>
+      </c>
+      <c r="D24" t="s">
+        <v>423</v>
       </c>
     </row>
   </sheetData>
@@ -5853,10 +7124,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>363</v>
+        <v>454</v>
       </c>
       <c r="B1" t="s">
-        <v>364</v>
+        <v>455</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -5864,7 +7135,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>365</v>
+        <v>456</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -5872,7 +7143,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>366</v>
+        <v>457</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -5880,7 +7151,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>367</v>
+        <v>458</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -5888,7 +7159,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>368</v>
+        <v>459</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -5896,7 +7167,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>369</v>
+        <v>460</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -5904,7 +7175,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>370</v>
+        <v>461</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -5912,7 +7183,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>371</v>
+        <v>462</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -5920,7 +7191,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>372</v>
+        <v>463</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -5928,7 +7199,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>373</v>
+        <v>280</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -5936,7 +7207,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>374</v>
+        <v>464</v>
       </c>
     </row>
   </sheetData>
@@ -5957,22 +7228,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>375</v>
+        <v>465</v>
       </c>
       <c r="B1" t="s">
-        <v>376</v>
+        <v>466</v>
       </c>
       <c r="C1" t="s">
-        <v>377</v>
+        <v>467</v>
       </c>
       <c r="D1" t="s">
-        <v>378</v>
+        <v>468</v>
       </c>
       <c r="E1" t="s">
-        <v>379</v>
+        <v>469</v>
       </c>
       <c r="F1" t="s">
-        <v>11</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -5980,19 +7251,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>380</v>
+        <v>470</v>
       </c>
       <c r="C2" t="s">
-        <v>381</v>
+        <v>471</v>
       </c>
       <c r="D2" t="s">
-        <v>382</v>
+        <v>472</v>
       </c>
       <c r="E2" t="s">
-        <v>383</v>
+        <v>473</v>
       </c>
       <c r="F2" t="s">
-        <v>384</v>
+        <v>474</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -6000,19 +7271,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>385</v>
+        <v>475</v>
       </c>
       <c r="C3" t="s">
-        <v>386</v>
+        <v>476</v>
       </c>
       <c r="D3" t="s">
-        <v>387</v>
+        <v>477</v>
       </c>
       <c r="E3" t="s">
-        <v>388</v>
+        <v>478</v>
       </c>
       <c r="F3" t="s">
-        <v>389</v>
+        <v>479</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -6020,19 +7291,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>390</v>
+        <v>480</v>
       </c>
       <c r="C4" t="s">
-        <v>391</v>
+        <v>481</v>
       </c>
       <c r="D4" t="s">
-        <v>392</v>
+        <v>482</v>
       </c>
       <c r="E4" t="s">
-        <v>393</v>
+        <v>483</v>
       </c>
       <c r="F4" t="s">
-        <v>394</v>
+        <v>484</v>
       </c>
     </row>
   </sheetData>
@@ -6053,16 +7324,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>395</v>
+        <v>485</v>
       </c>
       <c r="B1" t="s">
-        <v>396</v>
+        <v>486</v>
       </c>
       <c r="C1" t="s">
-        <v>379</v>
+        <v>469</v>
       </c>
       <c r="D1" t="s">
-        <v>397</v>
+        <v>487</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -6070,13 +7341,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>398</v>
+        <v>488</v>
       </c>
       <c r="C2" t="s">
-        <v>399</v>
+        <v>489</v>
       </c>
       <c r="D2" t="s">
-        <v>400</v>
+        <v>490</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -6084,13 +7355,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>401</v>
+        <v>491</v>
       </c>
       <c r="C3" t="s">
-        <v>294</v>
+        <v>353</v>
       </c>
       <c r="D3" t="s">
-        <v>402</v>
+        <v>492</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -6098,13 +7369,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>403</v>
+        <v>493</v>
       </c>
       <c r="C4" t="s">
-        <v>404</v>
+        <v>494</v>
       </c>
       <c r="D4" t="s">
-        <v>405</v>
+        <v>495</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -6112,13 +7383,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>406</v>
+        <v>496</v>
       </c>
       <c r="C5" t="s">
-        <v>407</v>
+        <v>497</v>
       </c>
       <c r="D5" t="s">
-        <v>408</v>
+        <v>498</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -6126,13 +7397,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>409</v>
+        <v>499</v>
       </c>
       <c r="C6" t="s">
-        <v>407</v>
+        <v>497</v>
       </c>
       <c r="D6" t="s">
-        <v>408</v>
+        <v>498</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -6140,13 +7411,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>410</v>
+        <v>500</v>
       </c>
       <c r="C7" t="s">
-        <v>411</v>
+        <v>501</v>
       </c>
       <c r="D7" t="s">
-        <v>412</v>
+        <v>502</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -6154,13 +7425,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>413</v>
+        <v>503</v>
       </c>
       <c r="C8" t="s">
-        <v>414</v>
+        <v>504</v>
       </c>
       <c r="D8" t="s">
-        <v>415</v>
+        <v>505</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -6168,13 +7439,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>416</v>
+        <v>506</v>
       </c>
       <c r="C9" t="s">
-        <v>414</v>
+        <v>504</v>
       </c>
       <c r="D9" t="s">
-        <v>417</v>
+        <v>507</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -6182,13 +7453,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>418</v>
+        <v>508</v>
       </c>
       <c r="C10" t="s">
-        <v>419</v>
+        <v>509</v>
       </c>
       <c r="D10" t="s">
-        <v>420</v>
+        <v>510</v>
       </c>
     </row>
   </sheetData>
@@ -6207,127 +7478,128 @@
     <col min="4" max="4" width="18.28515625" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="73.140625" style="1" customWidth="1"/>
     <col min="6" max="6" width="72.28515625" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="9.140625" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>421</v>
+        <v>511</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>379</v>
+        <v>469</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>422</v>
+        <v>512</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>34</v>
+        <v>73</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>423</v>
+        <v>513</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>424</v>
+        <v>514</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>425</v>
+        <v>515</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>426</v>
+        <v>516</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>428</v>
+        <v>518</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>429</v>
+        <v>519</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>430</v>
+        <v>520</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>431</v>
+        <v>521</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="90" x14ac:dyDescent="0.25">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>428</v>
+        <v>518</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>433</v>
+        <v>523</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>434</v>
+        <v>524</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>435</v>
+        <v>525</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>428</v>
+        <v>518</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>437</v>
+        <v>527</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>438</v>
+        <v>528</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>439</v>
+        <v>529</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>428</v>
+        <v>518</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>441</v>
+        <v>531</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>442</v>
+        <v>532</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>443</v>
+        <v>533</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>444</v>
+        <v>534</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -6335,19 +7607,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>428</v>
+        <v>518</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>445</v>
+        <v>535</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>446</v>
+        <v>536</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>447</v>
+        <v>537</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>448</v>
+        <v>538</v>
       </c>
     </row>
   </sheetData>
@@ -6366,198 +7638,205 @@
     <col min="5" max="5" width="56.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="65.85546875" style="2" customWidth="1"/>
-    <col min="9" max="16384" width="9.140625" style="2"/>
+    <col min="9" max="9" width="9.140625" style="2" customWidth="1"/>
+    <col min="10" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>449</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>450</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>451</v>
+        <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>452</v>
+        <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="90" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>454</v>
+        <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>455</v>
+        <v>7</v>
       </c>
       <c r="D2" s="1">
         <v>2020</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>456</v>
+        <v>8</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>458</v>
+        <v>10</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>459</v>
+        <v>11</v>
       </c>
       <c r="D3" s="1">
         <v>2018</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>460</v>
+        <v>12</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>462</v>
+        <v>14</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>463</v>
+        <v>15</v>
       </c>
       <c r="D4" s="1">
         <v>2016</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>464</v>
+        <v>16</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>466</v>
+        <v>18</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>467</v>
+        <v>19</v>
       </c>
       <c r="D5" s="1">
         <v>2018</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>468</v>
+        <v>20</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>469</v>
+        <v>21</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>470</v>
+        <v>22</v>
       </c>
       <c r="D6" s="1">
         <v>2021</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>471</v>
+        <v>23</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>473</v>
+        <v>25</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>474</v>
+        <v>26</v>
       </c>
       <c r="D7" s="1">
         <v>2021</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>475</v>
+        <v>27</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>515</v>
+        <v>28</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>512</v>
+        <v>29</v>
       </c>
       <c r="D8" s="1">
         <v>2026</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>513</v>
+        <v>30</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
       <c r="B9" s="1" t="s">
-        <v>518</v>
+        <v>32</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>516</v>
+        <v>33</v>
       </c>
       <c r="D9" s="1">
         <v>2026</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>517</v>
+        <v>34</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
       <c r="B10" s="1" t="s">
-        <v>522</v>
+        <v>35</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>521</v>
+        <v>36</v>
       </c>
       <c r="D10" s="1">
         <v>2026</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>523</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -6576,10 +7855,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="B1" t="s">
-        <v>336</v>
+        <v>417</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
